--- a/results/block3_results/label/Normal_2/branches/dataframes/dataset_RCA_B03_Normal_2.xlsx
+++ b/results/block3_results/label/Normal_2/branches/dataframes/dataset_RCA_B03_Normal_2.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>11.15912001892901</v>
+        <v>2.234827188619676</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="b">
@@ -604,14 +604,14 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>34.19156206107118</v>
+        <v>34.1859209565437</v>
       </c>
       <c r="L3" t="n">
         <v>1.302709809008924</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>1.361532670712998</v>
+        <v>1.810672454247252</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="b">
@@ -657,14 +657,14 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>13.70480619480816</v>
+        <v>13.70250628148309</v>
       </c>
       <c r="L4" t="n">
         <v>1.722098230136411</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>1.107254980884808</v>
+        <v>1.989848067740842</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="b">
@@ -710,14 +710,14 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>13.70480619480816</v>
+        <v>13.70250628148309</v>
       </c>
       <c r="L5" t="n">
         <v>1.774062408179734</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>1.107254980884808</v>
+        <v>1.989848067740842</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="b">
@@ -763,14 +763,14 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>10.07391314257579</v>
+        <v>10.08259890354299</v>
       </c>
       <c r="L6" t="n">
         <v>2.171853274078166</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>1.257088550825828</v>
+        <v>2.136167422974272</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="b">
@@ -816,14 +816,14 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>9.086312375561954</v>
+        <v>9.090161634267119</v>
       </c>
       <c r="L7" t="n">
         <v>2.316861176336878</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1.257088550825828</v>
+        <v>2.221112341003636</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="b">
@@ -869,14 +869,14 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>8.746824124790566</v>
+        <v>8.749064301757452</v>
       </c>
       <c r="L8" t="n">
         <v>2.378895253592505</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>1.257088550825828</v>
+        <v>2.221112341003636</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="b">
@@ -922,14 +922,14 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>8.218179902291242</v>
+        <v>8.220849820326881</v>
       </c>
       <c r="L9" t="n">
         <v>2.614675218047566</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>1.668579154133544</v>
+        <v>2.21950440022878</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="b">
@@ -975,14 +975,14 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>7.836770619901664</v>
+        <v>7.837917333184313</v>
       </c>
       <c r="L10" t="n">
         <v>2.820285072483101</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>1.668579154133544</v>
+        <v>2.228902580455803</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="b">
@@ -1028,14 +1028,14 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>7.162722102583384</v>
+        <v>7.28780610133979</v>
       </c>
       <c r="L11" t="n">
         <v>3.179483753756899</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>2.297674616284092</v>
+        <v>2.399449402253348</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="b">
@@ -1081,14 +1081,14 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>7.310981061882006</v>
+        <v>7.210862258994188</v>
       </c>
       <c r="L12" t="n">
         <v>3.276192027091027</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2.297674616284092</v>
+        <v>2.399449402253348</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="b">
@@ -1134,14 +1134,14 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>7.037492341720552</v>
+        <v>6.939120458610888</v>
       </c>
       <c r="L13" t="n">
         <v>3.408770346324458</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>2.458820606152787</v>
+        <v>2.53628906525354</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="b">
@@ -1187,14 +1187,14 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>7.037492341720552</v>
+        <v>6.939120458610888</v>
       </c>
       <c r="L14" t="n">
         <v>3.410367151442912</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>2.458820606152787</v>
+        <v>2.53628906525354</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="b">
@@ -1240,14 +1240,14 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>6.860158236481039</v>
+        <v>6.857521759342521</v>
       </c>
       <c r="L15" t="n">
         <v>3.623160504184361</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>2.460406747861397</v>
+        <v>2.567703330165187</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="b">
@@ -1293,14 +1293,14 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>6.860158236481039</v>
+        <v>6.857521759342521</v>
       </c>
       <c r="L16" t="n">
         <v>3.657464332188214</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>2.460406747861397</v>
+        <v>2.567703330165187</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="b">
@@ -1346,14 +1346,14 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>6.860158236481039</v>
+        <v>6.857521759342521</v>
       </c>
       <c r="L17" t="n">
         <v>3.657730815482823</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>2.460406747861397</v>
+        <v>2.567703330165187</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="b">
@@ -1399,14 +1399,14 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>6.462664551863797</v>
+        <v>6.503419128500871</v>
       </c>
       <c r="L18" t="n">
         <v>4.04739033988656</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>2.270371957171189</v>
+        <v>2.460272776605422</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="b">
@@ -1452,14 +1452,14 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>6.336005311670497</v>
+        <v>6.334333511993007</v>
       </c>
       <c r="L19" t="n">
         <v>4.214778929896502</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>2.271869422281108</v>
+        <v>2.460272776605422</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="b">
@@ -1505,14 +1505,14 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>6.336005311670497</v>
+        <v>6.334333511993007</v>
       </c>
       <c r="L20" t="n">
         <v>4.215876635134074</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>2.271869422281108</v>
+        <v>2.460272776605422</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="b">
@@ -1558,14 +1558,14 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>6.336005311670497</v>
+        <v>6.334333511993007</v>
       </c>
       <c r="L21" t="n">
         <v>4.232283232540341</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>2.271869422281108</v>
+        <v>2.460272776605422</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="b">
@@ -1611,14 +1611,14 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>6.667695648258961</v>
+        <v>6.6599124093544</v>
       </c>
       <c r="L22" t="n">
         <v>4.30763363275994</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>2.271869422281108</v>
+        <v>2.460272776605422</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="b">
@@ -1664,14 +1664,14 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>8.729501710970144</v>
+        <v>8.72269683556639</v>
       </c>
       <c r="L23" t="n">
         <v>4.66762886598611</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>2.216039524358943</v>
+        <v>2.336857632616919</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="b">
@@ -1717,14 +1717,14 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>9.435939359634485</v>
+        <v>9.430284900862308</v>
       </c>
       <c r="L24" t="n">
         <v>4.794667061639472</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>2.213941658042832</v>
+        <v>2.32909000814458</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="b">
@@ -1770,18 +1770,18 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>11.15912001892901</v>
+        <v>11.15375254245231</v>
       </c>
       <c r="L25" t="n">
         <v>5.100723584245738</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>2.274306125900985</v>
+        <v>2.256972399806862</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -1823,18 +1823,18 @@
         <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>1.227287714443503</v>
+        <v>1.227382935937412</v>
       </c>
       <c r="L26" t="n">
         <v>5.561113856486432</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>2.260946222053909</v>
+        <v>2.255753292983399</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
@@ -1876,26 +1876,20 @@
         <v>19</v>
       </c>
       <c r="K27" t="n">
-        <v>1.23193593309144</v>
+        <v>1.24106372156266</v>
       </c>
       <c r="L27" t="n">
         <v>5.733631740764735</v>
       </c>
-      <c r="M27" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>2.183887499719703</v>
-      </c>
-      <c r="O27" t="n">
-        <v>18.18772478039544</v>
-      </c>
+        <v>2.274494923648692</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>93.22655280984159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1935,26 +1929,20 @@
         <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>1.35533946875624</v>
+        <v>1.354896791708974</v>
       </c>
       <c r="L28" t="n">
         <v>6.038107089471678</v>
       </c>
-      <c r="M28" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>1.910386319788868</v>
-      </c>
-      <c r="O28" t="n">
-        <v>18.05097419043003</v>
-      </c>
+        <v>2.33992287022176</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>92.49159932057965</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1994,26 +1982,20 @@
         <v>19</v>
       </c>
       <c r="K29" t="n">
-        <v>1.35533946875624</v>
+        <v>1.354896791708974</v>
       </c>
       <c r="L29" t="n">
         <v>6.089547337114324</v>
       </c>
-      <c r="M29" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>1.910386319788868</v>
-      </c>
-      <c r="O29" t="n">
-        <v>18.05097419043003</v>
-      </c>
+        <v>2.33992287022176</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>92.49159932057965</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2053,26 +2035,20 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.377032682735515</v>
+        <v>1.361693057044747</v>
       </c>
       <c r="L30" t="n">
         <v>6.241067343192158</v>
       </c>
-      <c r="M30" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>1.810542151060285</v>
-      </c>
-      <c r="O30" t="n">
-        <v>18.00105210606573</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>92.35026555880307</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2112,26 +2088,20 @@
         <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>1.361532670712998</v>
+        <v>1.361693057044747</v>
       </c>
       <c r="L31" t="n">
         <v>6.242286328494681</v>
       </c>
-      <c r="M31" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>1.810542151060285</v>
-      </c>
-      <c r="O31" t="n">
-        <v>18.00105210606573</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>92.43637170377276</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2171,26 +2141,20 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.361532670712998</v>
+        <v>1.361693057044747</v>
       </c>
       <c r="L32" t="n">
         <v>6.29621228418374</v>
       </c>
-      <c r="M32" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>1.810542151060285</v>
-      </c>
-      <c r="O32" t="n">
-        <v>18.00105210606573</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>92.43637170377276</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2230,26 +2194,20 @@
         <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>1.361532670712998</v>
+        <v>1.361693057044747</v>
       </c>
       <c r="L33" t="n">
         <v>6.296866501984398</v>
       </c>
-      <c r="M33" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>1.810542151060285</v>
-      </c>
-      <c r="O33" t="n">
-        <v>18.00105210606573</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>92.43637170377276</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2289,26 +2247,20 @@
         <v>19</v>
       </c>
       <c r="K34" t="n">
-        <v>1.361532670712998</v>
+        <v>1.361693057044747</v>
       </c>
       <c r="L34" t="n">
         <v>6.339341229802555</v>
       </c>
-      <c r="M34" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>1.810542151060285</v>
-      </c>
-      <c r="O34" t="n">
-        <v>18.00105210606573</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>92.43637170377276</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2348,26 +2300,20 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.332550697377175</v>
+        <v>1.332198337799302</v>
       </c>
       <c r="L35" t="n">
         <v>6.357100841245253</v>
       </c>
-      <c r="M35" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>1.829812881081303</v>
-      </c>
-      <c r="O35" t="n">
-        <v>18.01068747107624</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>92.60133351646267</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2407,26 +2353,20 @@
         <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>1.332550697377175</v>
+        <v>1.332198337799302</v>
       </c>
       <c r="L36" t="n">
         <v>6.436029059005253</v>
       </c>
-      <c r="M36" t="n">
-        <v>34.19156206107118</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>1.829812881081303</v>
-      </c>
-      <c r="O36" t="n">
-        <v>18.01068747107624</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>92.60133351646267</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2466,26 +2406,20 @@
         <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>1.284651506328684</v>
+        <v>1.284636687860095</v>
       </c>
       <c r="L37" t="n">
         <v>6.530806666504064</v>
       </c>
-      <c r="M37" t="n">
-        <v>13.70480619480816</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>1.829812881081303</v>
-      </c>
-      <c r="O37" t="n">
-        <v>7.767309537944733</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>83.46079166727004</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2525,26 +2459,20 @@
         <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>1.107254980884808</v>
+        <v>1.107461427996592</v>
       </c>
       <c r="L38" t="n">
         <v>6.907507971420258</v>
       </c>
-      <c r="M38" t="n">
-        <v>13.70480619480816</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>1.991065770279512</v>
-      </c>
-      <c r="O38" t="n">
-        <v>7.847935982543838</v>
-      </c>
+        <v>2.584006862581848</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>85.89113133252266</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2584,26 +2512,20 @@
         <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>1.112638311549703</v>
+        <v>1.112797393379885</v>
       </c>
       <c r="L39" t="n">
         <v>6.969167990370586</v>
       </c>
-      <c r="M39" t="n">
-        <v>13.70480619480816</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>2.137351514017634</v>
-      </c>
-      <c r="O39" t="n">
-        <v>7.921078854412899</v>
-      </c>
+        <v>2.586709133287388</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>85.9534498772242</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2643,26 +2565,20 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>1.112638311549703</v>
+        <v>1.112797393379885</v>
       </c>
       <c r="L40" t="n">
         <v>6.983008040101961</v>
       </c>
-      <c r="M40" t="n">
-        <v>10.07391314257579</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>2.137351514017634</v>
-      </c>
-      <c r="O40" t="n">
-        <v>6.105632328296712</v>
-      </c>
+        <v>2.586709133287388</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>81.776853702881</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2702,26 +2618,20 @@
         <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>1.257088550825828</v>
+        <v>1.257408492792987</v>
       </c>
       <c r="L41" t="n">
         <v>7.33467222549031</v>
       </c>
-      <c r="M41" t="n">
-        <v>9.086312375561954</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>2.221422323211839</v>
-      </c>
-      <c r="O41" t="n">
-        <v>5.653867349386896</v>
-      </c>
+        <v>2.586709133287388</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>77.76586408660356</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2761,26 +2671,20 @@
         <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>1.318599484561683</v>
+        <v>1.318824427330396</v>
       </c>
       <c r="L42" t="n">
         <v>7.433750459225902</v>
       </c>
-      <c r="M42" t="n">
-        <v>8.746824124790566</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>2.221422323211839</v>
-      </c>
-      <c r="O42" t="n">
-        <v>5.484123224001202</v>
-      </c>
+        <v>2.54484718829641</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>75.95605658912172</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2820,26 +2724,20 @@
         <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>1.318599484561683</v>
+        <v>1.318824427330396</v>
       </c>
       <c r="L43" t="n">
         <v>7.434149819953698</v>
       </c>
-      <c r="M43" t="n">
-        <v>8.746824124790566</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>2.221422323211839</v>
-      </c>
-      <c r="O43" t="n">
-        <v>5.484123224001202</v>
-      </c>
+        <v>2.54484718829641</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>75.95605658912172</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2879,26 +2777,20 @@
         <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>1.668579154133544</v>
+        <v>1.668702471981479</v>
       </c>
       <c r="L44" t="n">
         <v>7.725498356491574</v>
       </c>
-      <c r="M44" t="n">
-        <v>7.836770619901664</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>2.215632077142135</v>
-      </c>
-      <c r="O44" t="n">
-        <v>5.0262013485219</v>
-      </c>
+        <v>2.500363114220298</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>66.80238139237622</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2938,26 +2830,20 @@
         <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>2.154789540514063</v>
+        <v>2.153908199193142</v>
       </c>
       <c r="L45" t="n">
         <v>8.141765081993171</v>
       </c>
-      <c r="M45" t="n">
-        <v>7.162722102583384</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>2.40130937562907</v>
-      </c>
-      <c r="O45" t="n">
-        <v>4.782015739106227</v>
-      </c>
+        <v>2.390129634984446</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>54.93972295212899</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2997,26 +2883,20 @@
         <v>19</v>
       </c>
       <c r="K46" t="n">
-        <v>2.297674616284092</v>
+        <v>2.29642073798828</v>
       </c>
       <c r="L46" t="n">
         <v>8.171125780671733</v>
       </c>
-      <c r="M46" t="n">
-        <v>7.162722102583384</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>2.40130937562907</v>
-      </c>
-      <c r="O46" t="n">
-        <v>4.782015739106227</v>
-      </c>
+        <v>2.339746983234845</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>51.95175545964359</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3056,26 +2936,20 @@
         <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>2.458820606152787</v>
+        <v>2.458253411048135</v>
       </c>
       <c r="L47" t="n">
         <v>8.410577934011988</v>
       </c>
-      <c r="M47" t="n">
-        <v>7.037492341720552</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>2.537929763195659</v>
-      </c>
-      <c r="O47" t="n">
-        <v>4.787711052458105</v>
-      </c>
+        <v>2.311422362296051</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>48.64308686944714</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3115,26 +2989,20 @@
         <v>19</v>
       </c>
       <c r="K48" t="n">
-        <v>2.460406747861397</v>
+        <v>2.460846652165882</v>
       </c>
       <c r="L48" t="n">
         <v>8.606534859385327</v>
       </c>
-      <c r="M48" t="n">
-        <v>6.860158236481039</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>2.568277899878588</v>
-      </c>
-      <c r="O48" t="n">
-        <v>4.714218068179813</v>
-      </c>
+        <v>2.45584612763724</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>47.80880493270489</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3174,26 +3042,20 @@
         <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>2.410618974223967</v>
+        <v>2.411319919634006</v>
       </c>
       <c r="L49" t="n">
         <v>8.735601987819823</v>
       </c>
-      <c r="M49" t="n">
-        <v>6.860158236481039</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>2.552397377840622</v>
-      </c>
-      <c r="O49" t="n">
-        <v>4.706277807160831</v>
-      </c>
+        <v>2.45584612763724</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>48.77865113368164</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3233,26 +3095,20 @@
         <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>2.270371957171189</v>
+        <v>2.270446541180712</v>
       </c>
       <c r="L50" t="n">
         <v>9.06960108100855</v>
       </c>
-      <c r="M50" t="n">
-        <v>6.462664551863797</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>2.458664129952975</v>
-      </c>
-      <c r="O50" t="n">
-        <v>4.460664340908385</v>
-      </c>
+        <v>2.482296945838069</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>49.10238063981199</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3292,26 +3148,20 @@
         <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>2.271869422281108</v>
+        <v>2.272052080753573</v>
       </c>
       <c r="L51" t="n">
         <v>9.184792874260843</v>
       </c>
-      <c r="M51" t="n">
-        <v>6.336005311670497</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>2.458664129952975</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.397334720811736</v>
-      </c>
+        <v>2.510379246784962</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>48.33530839649781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3351,26 +3201,20 @@
         <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>2.271869422281108</v>
+        <v>2.272052080753573</v>
       </c>
       <c r="L52" t="n">
         <v>9.223172384014479</v>
       </c>
-      <c r="M52" t="n">
-        <v>6.336005311670497</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>2.458664129952975</v>
-      </c>
-      <c r="O52" t="n">
-        <v>4.397334720811736</v>
-      </c>
+        <v>2.510379246784962</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>48.33530839649781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3410,26 +3254,20 @@
         <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>2.216039524358943</v>
+        <v>2.215926808664032</v>
       </c>
       <c r="L53" t="n">
         <v>9.484518214308473</v>
       </c>
-      <c r="M53" t="n">
-        <v>6.667695648258961</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>2.340751823293324</v>
-      </c>
-      <c r="O53" t="n">
-        <v>4.504223735776143</v>
-      </c>
+        <v>2.552119591261148</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>50.80085594422437</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3469,26 +3307,20 @@
         <v>19</v>
       </c>
       <c r="K54" t="n">
-        <v>2.216039524358943</v>
+        <v>2.215926808664032</v>
       </c>
       <c r="L54" t="n">
         <v>9.543591521947139</v>
       </c>
-      <c r="M54" t="n">
-        <v>8.729501710970144</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>2.340751823293324</v>
-      </c>
-      <c r="O54" t="n">
-        <v>5.535126767131734</v>
-      </c>
+        <v>2.555912126937463</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>59.96406916065483</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3528,26 +3360,20 @@
         <v>19</v>
       </c>
       <c r="K55" t="n">
-        <v>2.213941658042832</v>
+        <v>2.21383558243299</v>
       </c>
       <c r="L55" t="n">
         <v>9.872981036388081</v>
       </c>
-      <c r="M55" t="n">
-        <v>9.435939359634485</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>2.291460197292751</v>
-      </c>
-      <c r="O55" t="n">
-        <v>5.863699778463618</v>
-      </c>
+        <v>2.515616111885459</v>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>62.2432637807572</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3587,26 +3413,20 @@
         <v>19</v>
       </c>
       <c r="K56" t="n">
-        <v>2.235270250419494</v>
+        <v>2.234827188619676</v>
       </c>
       <c r="L56" t="n">
         <v>9.929850328282296</v>
       </c>
-      <c r="M56" t="n">
-        <v>9.435939359634485</v>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>2.291460197292751</v>
-      </c>
-      <c r="O56" t="n">
-        <v>5.863699778463618</v>
-      </c>
+        <v>2.515616111885459</v>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>61.87952427869406</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3646,26 +3466,20 @@
         <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>2.274306125900985</v>
+        <v>2.27411075658675</v>
       </c>
       <c r="L57" t="n">
         <v>10.20864362524451</v>
       </c>
-      <c r="M57" t="n">
-        <v>11.15912001892901</v>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>2.256392889218995</v>
-      </c>
-      <c r="O57" t="n">
-        <v>6.707756454074003</v>
-      </c>
+        <v>2.52834745651818</v>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="b">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>66.09438429268448</v>
-      </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3705,26 +3519,20 @@
         <v>19</v>
       </c>
       <c r="K58" t="n">
-        <v>2.274306125900985</v>
+        <v>2.27411075658675</v>
       </c>
       <c r="L58" t="n">
         <v>10.25290163967802</v>
       </c>
-      <c r="M58" t="n">
-        <v>11.15912001892901</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>2.252810073838055</v>
-      </c>
-      <c r="O58" t="n">
-        <v>6.705965046383533</v>
-      </c>
+        <v>2.533854113018922</v>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="b">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>66.08532686689892</v>
-      </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3764,26 +3572,20 @@
         <v>19</v>
       </c>
       <c r="K59" t="n">
-        <v>2.260946222053909</v>
+        <v>2.261921140867016</v>
       </c>
       <c r="L59" t="n">
         <v>10.49532189981052</v>
       </c>
-      <c r="M59" t="n">
-        <v>1.227287714443503</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>2.241589356169574</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1.734438535306539</v>
-      </c>
+        <v>2.531204737504585</v>
+      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="b">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>-30.35608792296103</v>
-      </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3823,26 +3625,20 @@
         <v>19</v>
       </c>
       <c r="K60" t="n">
-        <v>2.183887499719703</v>
+        <v>2.18573777095802</v>
       </c>
       <c r="L60" t="n">
         <v>10.64312708296901</v>
       </c>
-      <c r="M60" t="n">
-        <v>1.227287714443503</v>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>2.256258194428659</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1.741772954436081</v>
-      </c>
+        <v>2.516485706149343</v>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="b">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>-25.38301815730983</v>
-      </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3882,25 +3678,25 @@
         <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>1.970594865057129</v>
+        <v>1.971921957556851</v>
       </c>
       <c r="L61" t="n">
         <v>10.93995363377203</v>
       </c>
       <c r="M61" t="n">
-        <v>1.35533946875624</v>
+        <v>34.1859209565437</v>
       </c>
       <c r="N61" t="n">
-        <v>2.34160528784422</v>
+        <v>2.52260041570954</v>
       </c>
       <c r="O61" t="n">
-        <v>1.84847237830023</v>
+        <v>18.35426068612662</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>-6.606670902445244</v>
+        <v>89.25632586744634</v>
       </c>
     </row>
     <row r="62">
@@ -3941,25 +3737,25 @@
         <v>19</v>
       </c>
       <c r="K62" t="n">
-        <v>1.910386319788868</v>
+        <v>1.911918446699226</v>
       </c>
       <c r="L62" t="n">
         <v>11.0183957974736</v>
       </c>
       <c r="M62" t="n">
-        <v>1.35533946875624</v>
+        <v>34.1859209565437</v>
       </c>
       <c r="N62" t="n">
-        <v>2.34160528784422</v>
+        <v>2.543868584742552</v>
       </c>
       <c r="O62" t="n">
-        <v>1.84847237830023</v>
+        <v>18.36489477064313</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>-3.349465332317902</v>
+        <v>89.58927633086419</v>
       </c>
     </row>
     <row r="63">
@@ -4000,25 +3796,25 @@
         <v>19</v>
       </c>
       <c r="K63" t="n">
-        <v>1.810542151060285</v>
+        <v>1.810672454247252</v>
       </c>
       <c r="L63" t="n">
         <v>11.23844530909249</v>
       </c>
       <c r="M63" t="n">
-        <v>1.377032682735515</v>
+        <v>34.1859209565437</v>
       </c>
       <c r="N63" t="n">
-        <v>2.530274206826251</v>
+        <v>2.543868584742552</v>
       </c>
       <c r="O63" t="n">
-        <v>1.953653444780883</v>
+        <v>18.36489477064313</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.325316273616234</v>
+        <v>90.14057811460118</v>
       </c>
     </row>
     <row r="64">
@@ -4059,25 +3855,25 @@
         <v>19</v>
       </c>
       <c r="K64" t="n">
-        <v>1.829812881081303</v>
+        <v>1.829149160512111</v>
       </c>
       <c r="L64" t="n">
         <v>11.45649838827099</v>
       </c>
       <c r="M64" t="n">
-        <v>1.332550697377175</v>
+        <v>34.1859209565437</v>
       </c>
       <c r="N64" t="n">
-        <v>2.530274206826251</v>
+        <v>2.486985759527316</v>
       </c>
       <c r="O64" t="n">
-        <v>1.931412452101713</v>
+        <v>18.33645335803551</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.260376721184102</v>
+        <v>90.02452041953615</v>
       </c>
     </row>
     <row r="65">
@@ -4118,25 +3914,25 @@
         <v>19</v>
       </c>
       <c r="K65" t="n">
-        <v>1.829812881081303</v>
+        <v>1.829149160512111</v>
       </c>
       <c r="L65" t="n">
         <v>11.50163420872183</v>
       </c>
       <c r="M65" t="n">
-        <v>1.284651506328684</v>
+        <v>34.1859209565437</v>
       </c>
       <c r="N65" t="n">
-        <v>2.530274206826251</v>
+        <v>2.486985759527316</v>
       </c>
       <c r="O65" t="n">
-        <v>1.907462856577467</v>
+        <v>18.33645335803551</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.070851247687745</v>
+        <v>90.02452041953615</v>
       </c>
     </row>
     <row r="66">
@@ -4177,25 +3973,25 @@
         <v>19</v>
       </c>
       <c r="K66" t="n">
-        <v>1.991065770279512</v>
+        <v>1.989848067740842</v>
       </c>
       <c r="L66" t="n">
         <v>11.71523939062248</v>
       </c>
       <c r="M66" t="n">
-        <v>1.284651506328684</v>
+        <v>13.70250628148309</v>
       </c>
       <c r="N66" t="n">
-        <v>2.584584463834299</v>
+        <v>2.40495911174157</v>
       </c>
       <c r="O66" t="n">
-        <v>1.934617985081491</v>
+        <v>8.053732696612331</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>-2.917774239323156</v>
+        <v>75.2928468984594</v>
       </c>
     </row>
     <row r="67">
@@ -4236,25 +4032,25 @@
         <v>19</v>
       </c>
       <c r="K67" t="n">
-        <v>1.991065770279512</v>
+        <v>1.989848067740842</v>
       </c>
       <c r="L67" t="n">
         <v>11.80567174843549</v>
       </c>
       <c r="M67" t="n">
-        <v>1.107254980884808</v>
+        <v>13.70250628148309</v>
       </c>
       <c r="N67" t="n">
-        <v>2.584584463834299</v>
+        <v>2.40495911174157</v>
       </c>
       <c r="O67" t="n">
-        <v>1.845919722359553</v>
+        <v>8.053732696612331</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>-7.863074767651623</v>
+        <v>75.2928468984594</v>
       </c>
     </row>
     <row r="68">
@@ -4295,25 +4091,25 @@
         <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>2.137351514017634</v>
+        <v>2.136167422974272</v>
       </c>
       <c r="L68" t="n">
         <v>12.11875110916128</v>
       </c>
       <c r="M68" t="n">
-        <v>1.112638311549703</v>
+        <v>10.08259890354299</v>
       </c>
       <c r="N68" t="n">
-        <v>2.586206055763945</v>
+        <v>2.127609197394967</v>
       </c>
       <c r="O68" t="n">
-        <v>1.849422183656824</v>
+        <v>6.10510405046898</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>-15.56861018026146</v>
+        <v>65.01013897035585</v>
       </c>
     </row>
     <row r="69">
@@ -4354,25 +4150,25 @@
         <v>19</v>
       </c>
       <c r="K69" t="n">
-        <v>2.221422323211839</v>
+        <v>2.221112341003636</v>
       </c>
       <c r="L69" t="n">
         <v>12.34014777488538</v>
       </c>
       <c r="M69" t="n">
-        <v>1.257088550825828</v>
+        <v>9.090161634267119</v>
       </c>
       <c r="N69" t="n">
-        <v>2.544664688156764</v>
+        <v>2.020965165643478</v>
       </c>
       <c r="O69" t="n">
-        <v>1.900876619491296</v>
+        <v>5.555563399955298</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>-16.86304626158883</v>
+        <v>60.02003431332441</v>
       </c>
     </row>
     <row r="70">
@@ -4413,25 +4209,25 @@
         <v>19</v>
       </c>
       <c r="K70" t="n">
-        <v>2.219204132671578</v>
+        <v>2.21950440022878</v>
       </c>
       <c r="L70" t="n">
         <v>12.5694748975826</v>
       </c>
       <c r="M70" t="n">
-        <v>1.318599484561683</v>
+        <v>8.220849820326881</v>
       </c>
       <c r="N70" t="n">
-        <v>2.529506928743095</v>
+        <v>1.95763951878183</v>
       </c>
       <c r="O70" t="n">
-        <v>1.924053206652389</v>
+        <v>5.089244669554356</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>-15.34006050345738</v>
+        <v>56.38833374416772</v>
       </c>
     </row>
     <row r="71">
@@ -4472,25 +4268,25 @@
         <v>19</v>
       </c>
       <c r="K71" t="n">
-        <v>2.215632077142135</v>
+        <v>2.215315479264364</v>
       </c>
       <c r="L71" t="n">
         <v>12.7197557366194</v>
       </c>
       <c r="M71" t="n">
-        <v>1.668579154133544</v>
+        <v>7.837917333184313</v>
       </c>
       <c r="N71" t="n">
-        <v>2.497336168150439</v>
+        <v>1.91398474405841</v>
       </c>
       <c r="O71" t="n">
-        <v>2.082957661141991</v>
+        <v>4.875951038621362</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>-6.369520536841056</v>
+        <v>54.56649458295777</v>
       </c>
     </row>
     <row r="72">
@@ -4531,25 +4327,25 @@
         <v>19</v>
       </c>
       <c r="K72" t="n">
-        <v>2.229827140497467</v>
+        <v>2.228902580455803</v>
       </c>
       <c r="L72" t="n">
         <v>12.76423736081873</v>
       </c>
       <c r="M72" t="n">
-        <v>1.668579154133544</v>
+        <v>7.837917333184313</v>
       </c>
       <c r="N72" t="n">
-        <v>2.446076643315274</v>
+        <v>1.880763567036991</v>
       </c>
       <c r="O72" t="n">
-        <v>2.057327898724409</v>
+        <v>4.859340450110652</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>-8.384625604893214</v>
+        <v>54.13158219023224</v>
       </c>
     </row>
     <row r="73">
@@ -4590,25 +4386,25 @@
         <v>19</v>
       </c>
       <c r="K73" t="n">
-        <v>2.229827140497467</v>
+        <v>2.228902580455803</v>
       </c>
       <c r="L73" t="n">
         <v>12.77895579765649</v>
       </c>
       <c r="M73" t="n">
-        <v>1.668579154133544</v>
+        <v>7.837917333184313</v>
       </c>
       <c r="N73" t="n">
-        <v>2.446076643315274</v>
+        <v>1.880763567036991</v>
       </c>
       <c r="O73" t="n">
-        <v>2.057327898724409</v>
+        <v>4.859340450110652</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.384625604893214</v>
+        <v>54.13158219023224</v>
       </c>
     </row>
     <row r="74">
@@ -4649,25 +4445,25 @@
         <v>19</v>
       </c>
       <c r="K74" t="n">
-        <v>2.319870152035572</v>
+        <v>2.31824343275251</v>
       </c>
       <c r="L74" t="n">
         <v>12.95959142763117</v>
       </c>
       <c r="M74" t="n">
-        <v>2.154789540514063</v>
+        <v>7.837917333184313</v>
       </c>
       <c r="N74" t="n">
-        <v>2.411004224014718</v>
+        <v>1.833305263923982</v>
       </c>
       <c r="O74" t="n">
-        <v>2.28289688226439</v>
+        <v>4.835611298554148</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>-1.619576865622974</v>
+        <v>52.05893754434589</v>
       </c>
     </row>
     <row r="75">
@@ -4708,25 +4504,25 @@
         <v>19</v>
       </c>
       <c r="K75" t="n">
-        <v>2.40130937562907</v>
+        <v>2.399449402253348</v>
       </c>
       <c r="L75" t="n">
         <v>13.16300668342753</v>
       </c>
       <c r="M75" t="n">
-        <v>2.297674616284092</v>
+        <v>7.28780610133979</v>
       </c>
       <c r="N75" t="n">
-        <v>2.401508938888195</v>
+        <v>1.833305263923982</v>
       </c>
       <c r="O75" t="n">
-        <v>2.349591777586144</v>
+        <v>4.560555682631886</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>-2.201131215059782</v>
+        <v>47.38690700803743</v>
       </c>
     </row>
     <row r="76">
@@ -4767,25 +4563,25 @@
         <v>19</v>
       </c>
       <c r="K76" t="n">
-        <v>2.40130937562907</v>
+        <v>2.399449402253348</v>
       </c>
       <c r="L76" t="n">
         <v>13.23132399866896</v>
       </c>
       <c r="M76" t="n">
-        <v>2.297674616284092</v>
+        <v>7.210862258994188</v>
       </c>
       <c r="N76" t="n">
-        <v>2.355374210797699</v>
+        <v>1.835471097545149</v>
       </c>
       <c r="O76" t="n">
-        <v>2.326524413540896</v>
+        <v>4.523166678269669</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>-3.214449917349205</v>
+        <v>46.95200126537779</v>
       </c>
     </row>
     <row r="77">
@@ -4826,25 +4622,25 @@
         <v>19</v>
       </c>
       <c r="K77" t="n">
-        <v>2.537929763195659</v>
+        <v>2.53628906525354</v>
       </c>
       <c r="L77" t="n">
         <v>13.5365703437557</v>
       </c>
       <c r="M77" t="n">
-        <v>2.460406747861397</v>
+        <v>6.857521759342521</v>
       </c>
       <c r="N77" t="n">
-        <v>2.315226465388985</v>
+        <v>1.838170620522636</v>
       </c>
       <c r="O77" t="n">
-        <v>2.387816606625191</v>
+        <v>4.347846189932579</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>-6.286628384858672</v>
+        <v>41.66562121893116</v>
       </c>
     </row>
     <row r="78">
@@ -4885,25 +4681,25 @@
         <v>19</v>
       </c>
       <c r="K78" t="n">
-        <v>2.537929763195659</v>
+        <v>2.53628906525354</v>
       </c>
       <c r="L78" t="n">
         <v>13.54085849787424</v>
       </c>
       <c r="M78" t="n">
-        <v>2.460406747861397</v>
+        <v>6.857521759342521</v>
       </c>
       <c r="N78" t="n">
-        <v>2.457069773380443</v>
+        <v>1.838170620522636</v>
       </c>
       <c r="O78" t="n">
-        <v>2.45873826062092</v>
+        <v>4.347846189932579</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>-3.220818736303399</v>
+        <v>41.66562121893116</v>
       </c>
     </row>
     <row r="79">
@@ -4944,25 +4740,25 @@
         <v>19</v>
       </c>
       <c r="K79" t="n">
-        <v>2.568277899878588</v>
+        <v>2.567703330165187</v>
       </c>
       <c r="L79" t="n">
         <v>13.59151213905385</v>
       </c>
       <c r="M79" t="n">
-        <v>2.460406747861397</v>
+        <v>6.857521759342521</v>
       </c>
       <c r="N79" t="n">
-        <v>2.457069773380443</v>
+        <v>1.852734478318536</v>
       </c>
       <c r="O79" t="n">
-        <v>2.45873826062092</v>
+        <v>4.355128118830528</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>-4.455115902821016</v>
+        <v>41.04184170695105</v>
       </c>
     </row>
     <row r="80">
@@ -5003,25 +4799,25 @@
         <v>19</v>
       </c>
       <c r="K80" t="n">
-        <v>2.552397377840622</v>
+        <v>2.553200095302242</v>
       </c>
       <c r="L80" t="n">
         <v>13.74715964556939</v>
       </c>
       <c r="M80" t="n">
-        <v>2.410618974223967</v>
+        <v>6.857521759342521</v>
       </c>
       <c r="N80" t="n">
-        <v>2.457069773380443</v>
+        <v>1.852734478318536</v>
       </c>
       <c r="O80" t="n">
-        <v>2.433844373802205</v>
+        <v>4.355128118830528</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>-4.871018267006577</v>
+        <v>41.37485682079438</v>
       </c>
     </row>
     <row r="81">
@@ -5062,25 +4858,25 @@
         <v>19</v>
       </c>
       <c r="K81" t="n">
-        <v>2.552397377840622</v>
+        <v>2.553200095302242</v>
       </c>
       <c r="L81" t="n">
         <v>13.76792294011217</v>
       </c>
       <c r="M81" t="n">
-        <v>2.410618974223967</v>
+        <v>6.857521759342521</v>
       </c>
       <c r="N81" t="n">
-        <v>2.457069773380443</v>
+        <v>1.852734478318536</v>
       </c>
       <c r="O81" t="n">
-        <v>2.433844373802205</v>
+        <v>4.355128118830528</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>-4.871018267006577</v>
+        <v>41.37485682079438</v>
       </c>
     </row>
     <row r="82">
@@ -5121,25 +4917,25 @@
         <v>19</v>
       </c>
       <c r="K82" t="n">
-        <v>2.52490559672174</v>
+        <v>2.525998643457513</v>
       </c>
       <c r="L82" t="n">
         <v>13.91109430662946</v>
       </c>
       <c r="M82" t="n">
-        <v>2.270371957171189</v>
+        <v>6.503419128500871</v>
       </c>
       <c r="N82" t="n">
-        <v>2.482427983219213</v>
+        <v>1.914609353839869</v>
       </c>
       <c r="O82" t="n">
-        <v>2.376399970195201</v>
+        <v>4.209014241170371</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>-6.24918483374417</v>
+        <v>39.98598011977441</v>
       </c>
     </row>
     <row r="83">
@@ -5180,25 +4976,25 @@
         <v>19</v>
       </c>
       <c r="K83" t="n">
-        <v>2.458664129952975</v>
+        <v>2.460272776605422</v>
       </c>
       <c r="L83" t="n">
         <v>14.10133801338902</v>
       </c>
       <c r="M83" t="n">
-        <v>2.270371957171189</v>
+        <v>6.503419128500871</v>
       </c>
       <c r="N83" t="n">
-        <v>2.511628680011507</v>
+        <v>1.986039459425867</v>
       </c>
       <c r="O83" t="n">
-        <v>2.391000318591348</v>
+        <v>4.244729293963369</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>-2.829937362847823</v>
+        <v>42.03934794842412</v>
       </c>
     </row>
     <row r="84">
@@ -5239,25 +5035,25 @@
         <v>19</v>
       </c>
       <c r="K84" t="n">
-        <v>2.458664129952975</v>
+        <v>2.460272776605422</v>
       </c>
       <c r="L84" t="n">
         <v>14.13282272675221</v>
       </c>
       <c r="M84" t="n">
-        <v>2.271869422281108</v>
+        <v>6.334333511993007</v>
       </c>
       <c r="N84" t="n">
-        <v>2.511628680011507</v>
+        <v>1.986039459425867</v>
       </c>
       <c r="O84" t="n">
-        <v>2.391749051146308</v>
+        <v>4.160186485709437</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>-2.797746643804322</v>
+        <v>40.86147856456317</v>
       </c>
     </row>
     <row r="85">
@@ -5298,25 +5094,25 @@
         <v>19</v>
       </c>
       <c r="K85" t="n">
-        <v>2.340751823293324</v>
+        <v>2.340941256016772</v>
       </c>
       <c r="L85" t="n">
         <v>14.52228531395234</v>
       </c>
       <c r="M85" t="n">
-        <v>2.216039524358943</v>
+        <v>8.72269683556639</v>
       </c>
       <c r="N85" t="n">
-        <v>2.555830182603009</v>
+        <v>1.943612908866282</v>
       </c>
       <c r="O85" t="n">
-        <v>2.385934853480976</v>
+        <v>5.333154872216336</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.893724387391882</v>
+        <v>56.10588268845957</v>
       </c>
     </row>
     <row r="86">
@@ -5357,25 +5153,25 @@
         <v>19</v>
       </c>
       <c r="K86" t="n">
-        <v>2.336561586544111</v>
+        <v>2.336857632616919</v>
       </c>
       <c r="L86" t="n">
         <v>14.60963129016067</v>
       </c>
       <c r="M86" t="n">
-        <v>2.216039524358943</v>
+        <v>8.72269683556639</v>
       </c>
       <c r="N86" t="n">
-        <v>2.549148888523415</v>
+        <v>1.88775516460374</v>
       </c>
       <c r="O86" t="n">
-        <v>2.382594206441179</v>
+        <v>5.305226000085066</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.93203776675952</v>
+        <v>55.95177976245593</v>
       </c>
     </row>
     <row r="87">
@@ -5416,25 +5212,25 @@
         <v>19</v>
       </c>
       <c r="K87" t="n">
-        <v>2.328929626762258</v>
+        <v>2.32909000814458</v>
       </c>
       <c r="L87" t="n">
         <v>14.74631449265113</v>
       </c>
       <c r="M87" t="n">
-        <v>2.213941658042832</v>
+        <v>9.430284900862308</v>
       </c>
       <c r="N87" t="n">
-        <v>2.549148888523415</v>
+        <v>1.809336938530754</v>
       </c>
       <c r="O87" t="n">
-        <v>2.381545273283124</v>
+        <v>5.619810919696531</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.20930700378128</v>
+        <v>58.55572293399596</v>
       </c>
     </row>
     <row r="88">
@@ -5475,25 +5271,25 @@
         <v>19</v>
       </c>
       <c r="K88" t="n">
-        <v>2.291460197292751</v>
+        <v>2.292277987951941</v>
       </c>
       <c r="L88" t="n">
         <v>14.89749462229166</v>
       </c>
       <c r="M88" t="n">
-        <v>2.213941658042832</v>
+        <v>9.430284900862308</v>
       </c>
       <c r="N88" t="n">
-        <v>2.515759755719835</v>
+        <v>1.62660465915978</v>
       </c>
       <c r="O88" t="n">
-        <v>2.364850706881334</v>
+        <v>5.528444780011044</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.103388699127108</v>
+        <v>58.53665761047247</v>
       </c>
     </row>
     <row r="89">
@@ -5534,25 +5330,25 @@
         <v>19</v>
       </c>
       <c r="K89" t="n">
-        <v>2.291460197292751</v>
+        <v>2.292277987951941</v>
       </c>
       <c r="L89" t="n">
         <v>14.90181048655315</v>
       </c>
       <c r="M89" t="n">
-        <v>2.235270250419494</v>
+        <v>9.430284900862308</v>
       </c>
       <c r="N89" t="n">
-        <v>2.515759755719835</v>
+        <v>1.62660465915978</v>
       </c>
       <c r="O89" t="n">
-        <v>2.375515003069665</v>
+        <v>5.528444780011044</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.538382442051402</v>
+        <v>58.53665761047247</v>
       </c>
     </row>
     <row r="90">
@@ -5593,25 +5389,25 @@
         <v>19</v>
       </c>
       <c r="K90" t="n">
-        <v>2.291460197292751</v>
+        <v>2.292277987951941</v>
       </c>
       <c r="L90" t="n">
         <v>14.90185431408795</v>
       </c>
       <c r="M90" t="n">
-        <v>2.235270250419494</v>
+        <v>9.430284900862308</v>
       </c>
       <c r="N90" t="n">
-        <v>2.515759755719835</v>
+        <v>1.62660465915978</v>
       </c>
       <c r="O90" t="n">
-        <v>2.375515003069665</v>
+        <v>5.528444780011044</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.538382442051402</v>
+        <v>58.53665761047247</v>
       </c>
     </row>
     <row r="91">
@@ -5652,25 +5448,25 @@
         <v>19</v>
       </c>
       <c r="K91" t="n">
-        <v>2.256392889218995</v>
+        <v>2.256972399806862</v>
       </c>
       <c r="L91" t="n">
         <v>15.1779242781088</v>
       </c>
       <c r="M91" t="n">
-        <v>2.274306125900985</v>
+        <v>11.15375254245231</v>
       </c>
       <c r="N91" t="n">
-        <v>2.528679156446047</v>
+        <v>1.382072456968563</v>
       </c>
       <c r="O91" t="n">
-        <v>2.401492641173516</v>
+        <v>6.267912499710435</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>6.042065233379867</v>
+        <v>63.99164155672037</v>
       </c>
     </row>
     <row r="92">
@@ -5711,25 +5507,25 @@
         <v>19</v>
       </c>
       <c r="K92" t="n">
-        <v>2.252810073838055</v>
+        <v>2.253288682135747</v>
       </c>
       <c r="L92" t="n">
         <v>15.27887836962461</v>
       </c>
       <c r="M92" t="n">
-        <v>2.274306125900985</v>
+        <v>11.15375254245231</v>
       </c>
       <c r="N92" t="n">
-        <v>2.533869015876358</v>
+        <v>1.33559316674232</v>
       </c>
       <c r="O92" t="n">
-        <v>2.404087570888672</v>
+        <v>6.244672854597313</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>6.292511923544319</v>
+        <v>63.9166256647555</v>
       </c>
     </row>
     <row r="93">
@@ -5770,25 +5566,25 @@
         <v>19</v>
       </c>
       <c r="K93" t="n">
-        <v>2.252810073838055</v>
+        <v>2.253288682135747</v>
       </c>
       <c r="L93" t="n">
         <v>15.34083586527301</v>
       </c>
       <c r="M93" t="n">
-        <v>2.274306125900985</v>
+        <v>1.227382935937412</v>
       </c>
       <c r="N93" t="n">
-        <v>2.533869015876358</v>
+        <v>1.289724165900363</v>
       </c>
       <c r="O93" t="n">
-        <v>2.404087570888672</v>
+        <v>1.258553550918887</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>6.292511923544319</v>
+        <v>-79.03796628205369</v>
       </c>
     </row>
     <row r="94">
@@ -5829,25 +5625,25 @@
         <v>19</v>
       </c>
       <c r="K94" t="n">
-        <v>2.241589356169574</v>
+        <v>2.241708558609957</v>
       </c>
       <c r="L94" t="n">
         <v>15.43406542723449</v>
       </c>
       <c r="M94" t="n">
-        <v>2.260946222053909</v>
+        <v>1.227382935937412</v>
       </c>
       <c r="N94" t="n">
-        <v>2.530864023077452</v>
+        <v>1.289724165900363</v>
       </c>
       <c r="O94" t="n">
-        <v>2.39590512256568</v>
+        <v>1.258553550918887</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>6.440812907935833</v>
+        <v>-78.11785259143362</v>
       </c>
     </row>
     <row r="95">
@@ -5888,25 +5684,25 @@
         <v>19</v>
       </c>
       <c r="K95" t="n">
-        <v>2.256258194428659</v>
+        <v>2.255753292983399</v>
       </c>
       <c r="L95" t="n">
         <v>15.59068641929283</v>
       </c>
       <c r="M95" t="n">
-        <v>2.183887499719703</v>
+        <v>1.227382935937412</v>
       </c>
       <c r="N95" t="n">
-        <v>2.530864023077452</v>
+        <v>1.212551325507892</v>
       </c>
       <c r="O95" t="n">
-        <v>2.357375761398578</v>
+        <v>1.219967130722652</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.289412346800758</v>
+        <v>-84.90279255697612</v>
       </c>
     </row>
     <row r="96">
@@ -5947,25 +5743,25 @@
         <v>19</v>
       </c>
       <c r="K96" t="n">
-        <v>2.275320402532291</v>
+        <v>2.274494923648692</v>
       </c>
       <c r="L96" t="n">
         <v>15.77796947024416</v>
       </c>
       <c r="M96" t="n">
-        <v>2.183887499719703</v>
+        <v>1.24106372156266</v>
       </c>
       <c r="N96" t="n">
-        <v>2.516545216993899</v>
+        <v>1.206739525023695</v>
       </c>
       <c r="O96" t="n">
-        <v>2.350216358356801</v>
+        <v>1.223901623293177</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.186768552529151</v>
+        <v>-85.83968518063251</v>
       </c>
     </row>
     <row r="97">
@@ -6006,25 +5802,25 @@
         <v>19</v>
       </c>
       <c r="K97" t="n">
-        <v>2.275320402532291</v>
+        <v>2.302930674306835</v>
       </c>
       <c r="L97" t="n">
         <v>15.8593454538893</v>
       </c>
       <c r="M97" t="n">
-        <v>1.970594865057129</v>
+        <v>1.24106372156266</v>
       </c>
       <c r="N97" t="n">
-        <v>2.523017728759505</v>
+        <v>1.206739525023695</v>
       </c>
       <c r="O97" t="n">
-        <v>2.246806296908316</v>
+        <v>1.223901623293177</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="n">
-        <v>-1.269094966629325</v>
+        <v>-88.16305416037373</v>
       </c>
     </row>
     <row r="98">
@@ -6065,25 +5861,25 @@
         <v>19</v>
       </c>
       <c r="K98" t="n">
-        <v>2.34160528784422</v>
+        <v>2.33992287022176</v>
       </c>
       <c r="L98" t="n">
         <v>15.99587210301866</v>
       </c>
       <c r="M98" t="n">
-        <v>1.910386319788868</v>
+        <v>1.354896791708974</v>
       </c>
       <c r="N98" t="n">
-        <v>2.523017728759505</v>
+        <v>1.192412560549965</v>
       </c>
       <c r="O98" t="n">
-        <v>2.216702024274186</v>
+        <v>1.27365467612947</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>-5.634643817809937</v>
+        <v>-83.71721268535599</v>
       </c>
     </row>
     <row r="99">
@@ -6124,25 +5920,25 @@
         <v>19</v>
       </c>
       <c r="K99" t="n">
-        <v>2.34160528784422</v>
+        <v>2.33992287022176</v>
       </c>
       <c r="L99" t="n">
         <v>16.0130433669017</v>
       </c>
       <c r="M99" t="n">
-        <v>1.910386319788868</v>
+        <v>1.354896791708974</v>
       </c>
       <c r="N99" t="n">
-        <v>2.543958390346354</v>
+        <v>1.192412560549965</v>
       </c>
       <c r="O99" t="n">
-        <v>2.227172355067611</v>
+        <v>1.27365467612947</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>-5.13803669106403</v>
+        <v>-83.71721268535599</v>
       </c>
     </row>
     <row r="100">
@@ -6183,25 +5979,25 @@
         <v>19</v>
       </c>
       <c r="K100" t="n">
-        <v>2.530274206826251</v>
+        <v>2.528368514819499</v>
       </c>
       <c r="L100" t="n">
         <v>16.37818737677483</v>
       </c>
       <c r="M100" t="n">
-        <v>1.829812881081303</v>
+        <v>1.332198337799302</v>
       </c>
       <c r="N100" t="n">
-        <v>2.485677645008055</v>
+        <v>1.234632837280565</v>
       </c>
       <c r="O100" t="n">
-        <v>2.157745263044679</v>
+        <v>1.283415587539934</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="n">
-        <v>-17.26473231858314</v>
+        <v>-97.00310167386273</v>
       </c>
     </row>
     <row r="101">
@@ -6242,25 +6038,25 @@
         <v>19</v>
       </c>
       <c r="K101" t="n">
-        <v>2.530274206826251</v>
+        <v>2.528368514819499</v>
       </c>
       <c r="L101" t="n">
         <v>16.44478342598408</v>
       </c>
       <c r="M101" t="n">
-        <v>1.829812881081303</v>
+        <v>1.332198337799302</v>
       </c>
       <c r="N101" t="n">
-        <v>2.485677645008055</v>
+        <v>1.234632837280565</v>
       </c>
       <c r="O101" t="n">
-        <v>2.157745263044679</v>
+        <v>1.283415587539934</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>-17.26473231858314</v>
+        <v>-97.00310167386273</v>
       </c>
     </row>
     <row r="102">
@@ -6301,25 +6097,25 @@
         <v>19</v>
       </c>
       <c r="K102" t="n">
-        <v>2.584584463834299</v>
+        <v>2.584006862581848</v>
       </c>
       <c r="L102" t="n">
         <v>16.74801422175818</v>
       </c>
       <c r="M102" t="n">
-        <v>1.991065770279512</v>
+        <v>1.107461427996592</v>
       </c>
       <c r="N102" t="n">
-        <v>2.402168259650153</v>
+        <v>1.297041515423841</v>
       </c>
       <c r="O102" t="n">
-        <v>2.196617014964832</v>
+        <v>1.202251471710216</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>-17.66204332509358</v>
+        <v>-114.9306466563164</v>
       </c>
     </row>
     <row r="103">
@@ -6360,25 +6156,25 @@
         <v>19</v>
       </c>
       <c r="K103" t="n">
-        <v>2.586206055763945</v>
+        <v>2.586709133287388</v>
       </c>
       <c r="L103" t="n">
         <v>17.12865526448994</v>
       </c>
       <c r="M103" t="n">
-        <v>2.137351514017634</v>
+        <v>1.112797393379885</v>
       </c>
       <c r="N103" t="n">
-        <v>2.123036630767556</v>
+        <v>1.283448220578055</v>
       </c>
       <c r="O103" t="n">
-        <v>2.130194072392595</v>
+        <v>1.19812280697897</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="n">
-        <v>-21.40706282499254</v>
+        <v>-115.8968277892728</v>
       </c>
     </row>
     <row r="104">
@@ -6419,25 +6215,25 @@
         <v>19</v>
       </c>
       <c r="K104" t="n">
-        <v>2.586206055763945</v>
+        <v>2.586709133287388</v>
       </c>
       <c r="L104" t="n">
         <v>17.13183983079523</v>
       </c>
       <c r="M104" t="n">
-        <v>2.137351514017634</v>
+        <v>1.112797393379885</v>
       </c>
       <c r="N104" t="n">
-        <v>2.123036630767556</v>
+        <v>1.283448220578055</v>
       </c>
       <c r="O104" t="n">
-        <v>2.130194072392595</v>
+        <v>1.19812280697897</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>-21.40706282499254</v>
+        <v>-115.8968277892728</v>
       </c>
     </row>
     <row r="105">
@@ -6478,25 +6274,25 @@
         <v>19</v>
       </c>
       <c r="K105" t="n">
-        <v>2.586206055763945</v>
+        <v>2.586709133287388</v>
       </c>
       <c r="L105" t="n">
         <v>17.16535816450019</v>
       </c>
       <c r="M105" t="n">
-        <v>2.137351514017634</v>
+        <v>1.257408492792987</v>
       </c>
       <c r="N105" t="n">
-        <v>2.123036630767556</v>
+        <v>1.283448220578055</v>
       </c>
       <c r="O105" t="n">
-        <v>2.130194072392595</v>
+        <v>1.270428356685521</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="n">
-        <v>-21.40706282499254</v>
+        <v>-103.6092094194097</v>
       </c>
     </row>
     <row r="106">
@@ -6537,25 +6333,25 @@
         <v>19</v>
       </c>
       <c r="K106" t="n">
-        <v>2.544664688156764</v>
+        <v>2.54484718829641</v>
       </c>
       <c r="L106" t="n">
         <v>17.51017709346702</v>
       </c>
       <c r="M106" t="n">
-        <v>2.219204132671578</v>
+        <v>1.318824427330396</v>
       </c>
       <c r="N106" t="n">
-        <v>1.992580752593158</v>
+        <v>1.224959555379384</v>
       </c>
       <c r="O106" t="n">
-        <v>2.105892442632368</v>
+        <v>1.27189199135489</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
       </c>
       <c r="Q106" t="n">
-        <v>-20.8354537317172</v>
+        <v>-100.0835924429005</v>
       </c>
     </row>
     <row r="107">
@@ -6596,25 +6392,25 @@
         <v>19</v>
       </c>
       <c r="K107" t="n">
-        <v>2.529506928743095</v>
+        <v>2.530712990426041</v>
       </c>
       <c r="L107" t="n">
         <v>17.6064753719879</v>
       </c>
       <c r="M107" t="n">
-        <v>2.219204132671578</v>
+        <v>1.668702471981479</v>
       </c>
       <c r="N107" t="n">
-        <v>1.957100819987285</v>
+        <v>1.241736362431915</v>
       </c>
       <c r="O107" t="n">
-        <v>2.088152476329431</v>
+        <v>1.455219417206697</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>-21.1361218788716</v>
+        <v>-73.90593889159069</v>
       </c>
     </row>
     <row r="108">
@@ -6655,25 +6451,25 @@
         <v>19</v>
       </c>
       <c r="K108" t="n">
-        <v>2.497336168150439</v>
+        <v>2.500363114220298</v>
       </c>
       <c r="L108" t="n">
         <v>17.68185944383634</v>
       </c>
       <c r="M108" t="n">
-        <v>2.215632077142135</v>
+        <v>1.668702471981479</v>
       </c>
       <c r="N108" t="n">
-        <v>1.912286907795664</v>
+        <v>1.241736362431915</v>
       </c>
       <c r="O108" t="n">
-        <v>2.0639594924689</v>
+        <v>1.455219417206697</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
       </c>
       <c r="Q108" t="n">
-        <v>-20.99734404976796</v>
+        <v>-71.82035125807769</v>
       </c>
     </row>
     <row r="109">
@@ -6714,25 +6510,25 @@
         <v>19</v>
       </c>
       <c r="K109" t="n">
-        <v>2.446076643315274</v>
+        <v>2.451535302424364</v>
       </c>
       <c r="L109" t="n">
         <v>17.83014168586917</v>
       </c>
       <c r="M109" t="n">
-        <v>2.229827140497467</v>
+        <v>1.668702471981479</v>
       </c>
       <c r="N109" t="n">
-        <v>1.880302071203517</v>
+        <v>1.289442800577439</v>
       </c>
       <c r="O109" t="n">
-        <v>2.055064605850492</v>
+        <v>1.479072636279459</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>-19.02675158491969</v>
+        <v>-65.74813449264344</v>
       </c>
     </row>
     <row r="110">
@@ -6773,25 +6569,25 @@
         <v>19</v>
       </c>
       <c r="K110" t="n">
-        <v>2.411004224014718</v>
+        <v>2.411460941051728</v>
       </c>
       <c r="L110" t="n">
         <v>17.8926913112489</v>
       </c>
       <c r="M110" t="n">
-        <v>2.319870152035572</v>
+        <v>1.668702471981479</v>
       </c>
       <c r="N110" t="n">
-        <v>1.880302071203517</v>
+        <v>1.289442800577439</v>
       </c>
       <c r="O110" t="n">
-        <v>2.100086111619545</v>
+        <v>1.479072636279459</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
       </c>
       <c r="Q110" t="n">
-        <v>-14.80501731214248</v>
+        <v>-63.03870965510192</v>
       </c>
     </row>
     <row r="111">
@@ -6832,25 +6628,25 @@
         <v>19</v>
       </c>
       <c r="K111" t="n">
-        <v>2.401508938888195</v>
+        <v>2.390129634984446</v>
       </c>
       <c r="L111" t="n">
         <v>18.0493298804623</v>
       </c>
       <c r="M111" t="n">
-        <v>2.319870152035572</v>
+        <v>2.153908199193142</v>
       </c>
       <c r="N111" t="n">
-        <v>1.833191292616835</v>
+        <v>1.359042505236806</v>
       </c>
       <c r="O111" t="n">
-        <v>2.076530722326204</v>
+        <v>1.756475352214974</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
       </c>
       <c r="Q111" t="n">
-        <v>-15.65005579103298</v>
+        <v>-36.07533017587821</v>
       </c>
     </row>
     <row r="112">
@@ -6891,25 +6687,25 @@
         <v>19</v>
       </c>
       <c r="K112" t="n">
-        <v>2.401508938888195</v>
+        <v>2.390129634984446</v>
       </c>
       <c r="L112" t="n">
         <v>18.0499924089303</v>
       </c>
       <c r="M112" t="n">
-        <v>2.319870152035572</v>
+        <v>2.153908199193142</v>
       </c>
       <c r="N112" t="n">
-        <v>1.833191292616835</v>
+        <v>1.359042505236806</v>
       </c>
       <c r="O112" t="n">
-        <v>2.076530722326204</v>
+        <v>1.756475352214974</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>-15.65005579103298</v>
+        <v>-36.07533017587821</v>
       </c>
     </row>
     <row r="113">
@@ -6950,25 +6746,25 @@
         <v>19</v>
       </c>
       <c r="K113" t="n">
-        <v>2.355374210797699</v>
+        <v>2.339746983234845</v>
       </c>
       <c r="L113" t="n">
         <v>18.2804012904116</v>
       </c>
       <c r="M113" t="n">
-        <v>2.40130937562907</v>
+        <v>2.29642073798828</v>
       </c>
       <c r="N113" t="n">
-        <v>1.835108269023008</v>
+        <v>1.252221301150578</v>
       </c>
       <c r="O113" t="n">
-        <v>2.118208822326039</v>
+        <v>1.774321019569429</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>-11.19650649982775</v>
+        <v>-31.86717383321234</v>
       </c>
     </row>
     <row r="114">
@@ -7009,25 +6805,25 @@
         <v>19</v>
       </c>
       <c r="K114" t="n">
-        <v>2.355374210797699</v>
+        <v>2.339746983234845</v>
       </c>
       <c r="L114" t="n">
         <v>18.28115814019267</v>
       </c>
       <c r="M114" t="n">
-        <v>2.40130937562907</v>
+        <v>2.29642073798828</v>
       </c>
       <c r="N114" t="n">
-        <v>1.835108269023008</v>
+        <v>1.252221301150578</v>
       </c>
       <c r="O114" t="n">
-        <v>2.118208822326039</v>
+        <v>1.774321019569429</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>-11.19650649982775</v>
+        <v>-31.86717383321234</v>
       </c>
     </row>
     <row r="115">
@@ -7068,25 +6864,25 @@
         <v>19</v>
       </c>
       <c r="K115" t="n">
-        <v>2.315226465388985</v>
+        <v>2.311422362296051</v>
       </c>
       <c r="L115" t="n">
         <v>18.32991998036753</v>
       </c>
       <c r="M115" t="n">
-        <v>2.40130937562907</v>
+        <v>2.458253411048135</v>
       </c>
       <c r="N115" t="n">
-        <v>1.835108269023008</v>
+        <v>1.151677425181881</v>
       </c>
       <c r="O115" t="n">
-        <v>2.118208822326039</v>
+        <v>1.804965418115008</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
       </c>
       <c r="Q115" t="n">
-        <v>-9.301143541012969</v>
+        <v>-28.05909404679647</v>
       </c>
     </row>
     <row r="116">
@@ -7127,25 +6923,25 @@
         <v>19</v>
       </c>
       <c r="K116" t="n">
-        <v>2.315226465388985</v>
+        <v>2.311422362296051</v>
       </c>
       <c r="L116" t="n">
         <v>18.33884219764906</v>
       </c>
       <c r="M116" t="n">
-        <v>2.40130937562907</v>
+        <v>2.458253411048135</v>
       </c>
       <c r="N116" t="n">
-        <v>1.835108269023008</v>
+        <v>1.151677425181881</v>
       </c>
       <c r="O116" t="n">
-        <v>2.118208822326039</v>
+        <v>1.804965418115008</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>-9.301143541012969</v>
+        <v>-28.05909404679647</v>
       </c>
     </row>
     <row r="117">
@@ -7186,25 +6982,25 @@
         <v>19</v>
       </c>
       <c r="K117" t="n">
-        <v>2.457069773380443</v>
+        <v>2.45584612763724</v>
       </c>
       <c r="L117" t="n">
         <v>18.74023701783926</v>
       </c>
       <c r="M117" t="n">
-        <v>2.552397377840622</v>
+        <v>2.411319919634006</v>
       </c>
       <c r="N117" t="n">
-        <v>1.851183425352798</v>
+        <v>0.8843090081545558</v>
       </c>
       <c r="O117" t="n">
-        <v>2.20179040159671</v>
+        <v>1.647814463894281</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
       </c>
       <c r="Q117" t="n">
-        <v>-11.59417225175512</v>
+        <v>-49.036568220996</v>
       </c>
     </row>
     <row r="118">
@@ -7245,25 +7041,25 @@
         <v>19</v>
       </c>
       <c r="K118" t="n">
-        <v>2.457069773380443</v>
+        <v>2.45584612763724</v>
       </c>
       <c r="L118" t="n">
         <v>18.75472837946535</v>
       </c>
       <c r="M118" t="n">
-        <v>2.552397377840622</v>
+        <v>2.411319919634006</v>
       </c>
       <c r="N118" t="n">
-        <v>1.851183425352798</v>
+        <v>0.8843090081545558</v>
       </c>
       <c r="O118" t="n">
-        <v>2.20179040159671</v>
+        <v>1.647814463894281</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
       </c>
       <c r="Q118" t="n">
-        <v>-11.59417225175512</v>
+        <v>-49.036568220996</v>
       </c>
     </row>
     <row r="119">
@@ -7304,25 +7100,25 @@
         <v>19</v>
       </c>
       <c r="K119" t="n">
-        <v>2.482427983219213</v>
+        <v>2.482296945838069</v>
       </c>
       <c r="L119" t="n">
         <v>18.93547697315022</v>
       </c>
       <c r="M119" t="n">
-        <v>2.52490559672174</v>
+        <v>2.270446541180712</v>
       </c>
       <c r="N119" t="n">
-        <v>1.918307120376766</v>
+        <v>0.8918796143983428</v>
       </c>
       <c r="O119" t="n">
-        <v>2.221606358549253</v>
+        <v>1.581163077789527</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>-11.74022678078219</v>
+        <v>-56.99183599128376</v>
       </c>
     </row>
     <row r="120">
@@ -7363,25 +7159,25 @@
         <v>19</v>
       </c>
       <c r="K120" t="n">
-        <v>2.511628680011507</v>
+        <v>2.510379246784962</v>
       </c>
       <c r="L120" t="n">
         <v>19.21762084673841</v>
       </c>
       <c r="M120" t="n">
-        <v>2.458664129952975</v>
+        <v>2.272052080753573</v>
       </c>
       <c r="N120" t="n">
-        <v>1.985832791947801</v>
+        <v>1.143035239705504</v>
       </c>
       <c r="O120" t="n">
-        <v>2.222248460950388</v>
+        <v>1.707543660229538</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
       </c>
       <c r="Q120" t="n">
-        <v>-13.0219561019455</v>
+        <v>-47.01698734001929</v>
       </c>
     </row>
     <row r="121">
@@ -7422,25 +7218,25 @@
         <v>19</v>
       </c>
       <c r="K121" t="n">
-        <v>2.552545134477885</v>
+        <v>2.552119591261148</v>
       </c>
       <c r="L121" t="n">
         <v>19.45385156025911</v>
       </c>
       <c r="M121" t="n">
-        <v>2.340751823293324</v>
+        <v>2.215926808664032</v>
       </c>
       <c r="N121" t="n">
-        <v>1.94111181613984</v>
+        <v>1.208876145314666</v>
       </c>
       <c r="O121" t="n">
-        <v>2.140931819716582</v>
+        <v>1.712401476989349</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
       </c>
       <c r="Q121" t="n">
-        <v>-19.22589551757854</v>
+        <v>-49.03745561748436</v>
       </c>
     </row>
     <row r="122">
@@ -7481,25 +7277,25 @@
         <v>19</v>
       </c>
       <c r="K122" t="n">
-        <v>2.555830182603009</v>
+        <v>2.555912126937463</v>
       </c>
       <c r="L122" t="n">
         <v>19.53079670328403</v>
       </c>
       <c r="M122" t="n">
-        <v>2.340751823293324</v>
+        <v>2.215926808664032</v>
       </c>
       <c r="N122" t="n">
-        <v>1.884597235153793</v>
+        <v>1.208876145314666</v>
       </c>
       <c r="O122" t="n">
-        <v>2.112674529223558</v>
+        <v>1.712401476989349</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
       </c>
       <c r="Q122" t="n">
-        <v>-20.97604942216622</v>
+        <v>-49.25893029659889</v>
       </c>
     </row>
     <row r="123">
@@ -7540,25 +7336,25 @@
         <v>19</v>
       </c>
       <c r="K123" t="n">
-        <v>2.549148888523415</v>
+        <v>2.54962759680487</v>
       </c>
       <c r="L123" t="n">
         <v>19.62393218445899</v>
       </c>
       <c r="M123" t="n">
-        <v>2.336561586544111</v>
+        <v>2.215926808664032</v>
       </c>
       <c r="N123" t="n">
-        <v>1.884597235153793</v>
+        <v>1.265348069603777</v>
       </c>
       <c r="O123" t="n">
-        <v>2.110579410848952</v>
+        <v>1.740637439133905</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
       </c>
       <c r="Q123" t="n">
-        <v>-20.77957718245978</v>
+        <v>-46.47666076132988</v>
       </c>
     </row>
     <row r="124">
@@ -7599,25 +7395,25 @@
         <v>19</v>
       </c>
       <c r="K124" t="n">
-        <v>2.515759755719835</v>
+        <v>2.515616111885459</v>
       </c>
       <c r="L124" t="n">
         <v>19.91511074534673</v>
       </c>
       <c r="M124" t="n">
-        <v>2.291460197292751</v>
+        <v>2.234827188619676</v>
       </c>
       <c r="N124" t="n">
-        <v>1.621958698060077</v>
+        <v>1.298981901047366</v>
       </c>
       <c r="O124" t="n">
-        <v>1.956709447676414</v>
+        <v>1.766904544833521</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
       </c>
       <c r="Q124" t="n">
-        <v>-28.57094131718389</v>
+        <v>-42.37419442047348</v>
       </c>
     </row>
     <row r="125">
@@ -7658,25 +7454,25 @@
         <v>19</v>
       </c>
       <c r="K125" t="n">
-        <v>2.528679156446047</v>
+        <v>2.52834745651818</v>
       </c>
       <c r="L125" t="n">
         <v>20.16223560691963</v>
       </c>
       <c r="M125" t="n">
-        <v>2.256392889218995</v>
+        <v>2.27411075658675</v>
       </c>
       <c r="N125" t="n">
-        <v>1.379798047976322</v>
+        <v>1.287600716901656</v>
       </c>
       <c r="O125" t="n">
-        <v>1.818095468597659</v>
+        <v>1.780855736744203</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>-39.08395901764601</v>
+        <v>-41.97373792559733</v>
       </c>
     </row>
     <row r="126">
@@ -7717,25 +7513,25 @@
         <v>19</v>
       </c>
       <c r="K126" t="n">
-        <v>2.533869015876358</v>
+        <v>2.533854113018922</v>
       </c>
       <c r="L126" t="n">
         <v>20.3178556048729</v>
       </c>
       <c r="M126" t="n">
-        <v>2.252810073838055</v>
+        <v>2.27411075658675</v>
       </c>
       <c r="N126" t="n">
-        <v>1.333362209138855</v>
+        <v>1.234526023781353</v>
       </c>
       <c r="O126" t="n">
-        <v>1.793086141488455</v>
+        <v>1.754318390184051</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>-41.31328982181373</v>
+        <v>-44.43524774046785</v>
       </c>
     </row>
     <row r="127">
@@ -7776,25 +7572,25 @@
         <v>19</v>
       </c>
       <c r="K127" t="n">
-        <v>2.530864023077452</v>
+        <v>2.531204737504585</v>
       </c>
       <c r="L127" t="n">
         <v>20.50329724155617</v>
       </c>
       <c r="M127" t="n">
-        <v>2.241589356169574</v>
+        <v>2.261921140867016</v>
       </c>
       <c r="N127" t="n">
-        <v>1.287433504266253</v>
+        <v>1.135750742934406</v>
       </c>
       <c r="O127" t="n">
-        <v>1.764511430217914</v>
+        <v>1.698835941900711</v>
       </c>
       <c r="P127" t="b">
         <v>1</v>
       </c>
       <c r="Q127" t="n">
-        <v>-43.43143261842715</v>
+        <v>-48.9964201412288</v>
       </c>
     </row>
     <row r="128">
@@ -7835,25 +7631,25 @@
         <v>19</v>
       </c>
       <c r="K128" t="n">
-        <v>2.516545216993899</v>
+        <v>2.516485706149343</v>
       </c>
       <c r="L128" t="n">
         <v>20.7310266058054</v>
       </c>
       <c r="M128" t="n">
-        <v>2.275320402532291</v>
+        <v>2.18573777095802</v>
       </c>
       <c r="N128" t="n">
-        <v>1.211808301441334</v>
+        <v>0.9438187947621866</v>
       </c>
       <c r="O128" t="n">
-        <v>1.743564351986812</v>
+        <v>1.564778282860103</v>
       </c>
       <c r="P128" t="b">
         <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>-44.33337170069264</v>
+        <v>-60.82059252188164</v>
       </c>
     </row>
     <row r="129">
@@ -7894,25 +7690,25 @@
         <v>19</v>
       </c>
       <c r="K129" t="n">
-        <v>2.516545216993899</v>
+        <v>2.516485706149343</v>
       </c>
       <c r="L129" t="n">
         <v>20.74639116271227</v>
       </c>
       <c r="M129" t="n">
-        <v>2.275320402532291</v>
+        <v>2.18573777095802</v>
       </c>
       <c r="N129" t="n">
-        <v>1.211808301441334</v>
+        <v>0.9438187947621866</v>
       </c>
       <c r="O129" t="n">
-        <v>1.743564351986812</v>
+        <v>1.564778282860103</v>
       </c>
       <c r="P129" t="b">
         <v>1</v>
       </c>
       <c r="Q129" t="n">
-        <v>-44.33337170069264</v>
+        <v>-60.82059252188164</v>
       </c>
     </row>
     <row r="130">
@@ -7953,25 +7749,25 @@
         <v>19</v>
       </c>
       <c r="K130" t="n">
-        <v>2.516545216993899</v>
+        <v>2.52260041570954</v>
       </c>
       <c r="L130" t="n">
         <v>20.80779055995246</v>
       </c>
       <c r="M130" t="n">
-        <v>2.275320402532291</v>
+        <v>1.971921957556851</v>
       </c>
       <c r="N130" t="n">
-        <v>1.205523507937499</v>
+        <v>0.9438187947621866</v>
       </c>
       <c r="O130" t="n">
-        <v>1.740421955234895</v>
+        <v>1.457870376159518</v>
       </c>
       <c r="P130" t="b">
         <v>1</v>
       </c>
       <c r="Q130" t="n">
-        <v>-44.59397098643561</v>
+        <v>-73.03324472199304</v>
       </c>
     </row>
     <row r="131">
@@ -8012,25 +7808,25 @@
         <v>19</v>
       </c>
       <c r="K131" t="n">
-        <v>2.523017728759505</v>
+        <v>2.52260041570954</v>
       </c>
       <c r="L131" t="n">
         <v>20.83060933287896</v>
       </c>
       <c r="M131" t="n">
-        <v>2.275320402532291</v>
+        <v>1.971921957556851</v>
       </c>
       <c r="N131" t="n">
-        <v>1.205523507937499</v>
+        <v>0.9438187947621866</v>
       </c>
       <c r="O131" t="n">
-        <v>1.740421955234895</v>
+        <v>1.457870376159518</v>
       </c>
       <c r="P131" t="b">
         <v>1</v>
       </c>
       <c r="Q131" t="n">
-        <v>-44.96586423600863</v>
+        <v>-73.03324472199304</v>
       </c>
     </row>
     <row r="132">
@@ -8071,25 +7867,25 @@
         <v>19</v>
       </c>
       <c r="K132" t="n">
-        <v>2.543958390346354</v>
+        <v>2.543868584742552</v>
       </c>
       <c r="L132" t="n">
         <v>21.16115091950983</v>
       </c>
       <c r="M132" t="n">
-        <v>2.34160528784422</v>
+        <v>1.810672454247252</v>
       </c>
       <c r="N132" t="n">
-        <v>1.16536180842725</v>
+        <v>0.7391853344810749</v>
       </c>
       <c r="O132" t="n">
-        <v>1.753483548135735</v>
+        <v>1.274928894364163</v>
       </c>
       <c r="P132" t="b">
         <v>1</v>
       </c>
       <c r="Q132" t="n">
-        <v>-45.08025427732325</v>
+        <v>-99.53023231238613</v>
       </c>
     </row>
     <row r="133">
@@ -8130,25 +7926,25 @@
         <v>19</v>
       </c>
       <c r="K133" t="n">
-        <v>2.543958390346354</v>
+        <v>2.543868584742552</v>
       </c>
       <c r="L133" t="n">
         <v>21.19442451795295</v>
       </c>
       <c r="M133" t="n">
-        <v>2.34160528784422</v>
+        <v>1.810672454247252</v>
       </c>
       <c r="N133" t="n">
-        <v>1.16536180842725</v>
+        <v>0.7391853344810749</v>
       </c>
       <c r="O133" t="n">
-        <v>1.753483548135735</v>
+        <v>1.274928894364163</v>
       </c>
       <c r="P133" t="b">
         <v>1</v>
       </c>
       <c r="Q133" t="n">
-        <v>-45.08025427732325</v>
+        <v>-99.53023231238613</v>
       </c>
     </row>
     <row r="134">
@@ -8189,25 +7985,25 @@
         <v>19</v>
       </c>
       <c r="K134" t="n">
-        <v>2.485677645008055</v>
+        <v>2.486985759527316</v>
       </c>
       <c r="L134" t="n">
         <v>21.50420978268466</v>
       </c>
       <c r="M134" t="n">
-        <v>2.530274206826251</v>
+        <v>1.829149160512111</v>
       </c>
       <c r="N134" t="n">
-        <v>1.236228494084955</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="O134" t="n">
-        <v>1.883251350455603</v>
+        <v>1.190760571206434</v>
       </c>
       <c r="P134" t="b">
         <v>1</v>
       </c>
       <c r="Q134" t="n">
-        <v>-31.98862936732851</v>
+        <v>-108.8569121001038</v>
       </c>
     </row>
     <row r="135">
@@ -8248,25 +8044,25 @@
         <v>19</v>
       </c>
       <c r="K135" t="n">
-        <v>2.485677645008055</v>
+        <v>2.453235713426281</v>
       </c>
       <c r="L135" t="n">
         <v>21.51868054601826</v>
       </c>
       <c r="M135" t="n">
-        <v>2.530274206826251</v>
+        <v>1.829149160512111</v>
       </c>
       <c r="N135" t="n">
-        <v>1.236228494084955</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="O135" t="n">
-        <v>1.883251350455603</v>
+        <v>1.190760571206434</v>
       </c>
       <c r="P135" t="b">
         <v>1</v>
       </c>
       <c r="Q135" t="n">
-        <v>-31.98862936732851</v>
+        <v>-106.0225852910762</v>
       </c>
     </row>
     <row r="136">
@@ -8307,25 +8103,25 @@
         <v>19</v>
       </c>
       <c r="K136" t="n">
-        <v>2.451207524165408</v>
+        <v>2.453235713426281</v>
       </c>
       <c r="L136" t="n">
         <v>21.5264914067186</v>
       </c>
       <c r="M136" t="n">
-        <v>2.530274206826251</v>
+        <v>1.829149160512111</v>
       </c>
       <c r="N136" t="n">
-        <v>1.236228494084955</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="O136" t="n">
-        <v>1.883251350455603</v>
+        <v>1.190760571206434</v>
       </c>
       <c r="P136" t="b">
         <v>1</v>
       </c>
       <c r="Q136" t="n">
-        <v>-30.15827778763587</v>
+        <v>-106.0225852910762</v>
       </c>
     </row>
     <row r="137">
@@ -8366,25 +8162,25 @@
         <v>19</v>
       </c>
       <c r="K137" t="n">
-        <v>2.402168259650153</v>
+        <v>2.40495911174157</v>
       </c>
       <c r="L137" t="n">
         <v>21.67701770906454</v>
       </c>
       <c r="M137" t="n">
-        <v>2.584584463834299</v>
+        <v>1.989848067740842</v>
       </c>
       <c r="N137" t="n">
-        <v>1.260336599441735</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="O137" t="n">
-        <v>1.922460531638017</v>
+        <v>1.271110024820799</v>
       </c>
       <c r="P137" t="b">
         <v>1</v>
       </c>
       <c r="Q137" t="n">
-        <v>-24.9527998165666</v>
+        <v>-89.20149041233627</v>
       </c>
     </row>
     <row r="138">
@@ -8425,25 +8221,25 @@
         <v>19</v>
       </c>
       <c r="K138" t="n">
-        <v>2.402168259650153</v>
+        <v>2.40495911174157</v>
       </c>
       <c r="L138" t="n">
         <v>21.69812778464038</v>
       </c>
       <c r="M138" t="n">
-        <v>2.584584463834299</v>
+        <v>1.989848067740842</v>
       </c>
       <c r="N138" t="n">
-        <v>1.260336599441735</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="O138" t="n">
-        <v>1.922460531638017</v>
+        <v>1.271110024820799</v>
       </c>
       <c r="P138" t="b">
         <v>1</v>
       </c>
       <c r="Q138" t="n">
-        <v>-24.9527998165666</v>
+        <v>-89.20149041233627</v>
       </c>
     </row>
     <row r="139">
@@ -8484,26 +8280,20 @@
         <v>19</v>
       </c>
       <c r="K139" t="n">
-        <v>2.190765346481614</v>
+        <v>2.194344862432881</v>
       </c>
       <c r="L139" t="n">
         <v>22.07100705499884</v>
       </c>
       <c r="M139" t="n">
-        <v>2.586206055763945</v>
-      </c>
-      <c r="N139" t="n">
-        <v>1.281377167733944</v>
-      </c>
-      <c r="O139" t="n">
-        <v>1.933791611748945</v>
-      </c>
+        <v>2.136167422974272</v>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
       <c r="P139" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>-13.28859496397645</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8543,26 +8333,20 @@
         <v>19</v>
       </c>
       <c r="K140" t="n">
-        <v>2.123036630767556</v>
+        <v>2.127609197394967</v>
       </c>
       <c r="L140" t="n">
         <v>22.12989523737562</v>
       </c>
       <c r="M140" t="n">
-        <v>2.586206055763945</v>
-      </c>
-      <c r="N140" t="n">
-        <v>1.281377167733944</v>
-      </c>
-      <c r="O140" t="n">
-        <v>1.933791611748945</v>
-      </c>
+        <v>2.136167422974272</v>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
       <c r="P140" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>-9.78621573642342</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8602,26 +8386,20 @@
         <v>19</v>
       </c>
       <c r="K141" t="n">
-        <v>2.019402621132054</v>
+        <v>2.020965165643478</v>
       </c>
       <c r="L141" t="n">
         <v>22.35251490711774</v>
       </c>
       <c r="M141" t="n">
-        <v>2.544664688156764</v>
-      </c>
-      <c r="N141" t="n">
-        <v>1.227335525810869</v>
-      </c>
-      <c r="O141" t="n">
-        <v>1.886000106983816</v>
-      </c>
+        <v>2.221112341003636</v>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
       <c r="P141" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>-7.073303636317463</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8661,26 +8439,20 @@
         <v>19</v>
       </c>
       <c r="K142" t="n">
-        <v>1.992580752593158</v>
+        <v>1.992690625306859</v>
       </c>
       <c r="L142" t="n">
         <v>22.47768594948983</v>
       </c>
       <c r="M142" t="n">
-        <v>2.544664688156764</v>
-      </c>
-      <c r="N142" t="n">
-        <v>1.227335525810869</v>
-      </c>
-      <c r="O142" t="n">
-        <v>1.886000106983816</v>
-      </c>
+        <v>2.21950440022878</v>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
       <c r="P142" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>-5.651147378766108</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8720,26 +8492,20 @@
         <v>19</v>
       </c>
       <c r="K143" t="n">
-        <v>1.992580752593158</v>
+        <v>1.992690625306859</v>
       </c>
       <c r="L143" t="n">
         <v>22.47841570416758</v>
       </c>
       <c r="M143" t="n">
-        <v>2.544664688156764</v>
-      </c>
-      <c r="N143" t="n">
-        <v>1.227335525810869</v>
-      </c>
-      <c r="O143" t="n">
-        <v>1.886000106983816</v>
-      </c>
+        <v>2.21950440022878</v>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
       <c r="P143" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>-5.651147378766108</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8779,26 +8545,20 @@
         <v>19</v>
       </c>
       <c r="K144" t="n">
-        <v>1.957100819987285</v>
+        <v>1.95763951878183</v>
       </c>
       <c r="L144" t="n">
         <v>22.62010036014249</v>
       </c>
       <c r="M144" t="n">
-        <v>2.529506928743095</v>
-      </c>
-      <c r="N144" t="n">
-        <v>1.243950820717568</v>
-      </c>
-      <c r="O144" t="n">
-        <v>1.886728874730332</v>
-      </c>
+        <v>2.21950440022878</v>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
       <c r="P144" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>-3.729838780731609</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8838,26 +8598,20 @@
         <v>19</v>
       </c>
       <c r="K145" t="n">
-        <v>1.912286907795664</v>
+        <v>1.91398474405841</v>
       </c>
       <c r="L145" t="n">
         <v>22.66055816100948</v>
       </c>
       <c r="M145" t="n">
-        <v>2.497336168150439</v>
-      </c>
-      <c r="N145" t="n">
-        <v>1.243950820717568</v>
-      </c>
-      <c r="O145" t="n">
-        <v>1.870643494434004</v>
-      </c>
+        <v>2.215315479264364</v>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
       <c r="P145" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>-2.22615444821892</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8897,26 +8651,20 @@
         <v>19</v>
       </c>
       <c r="K146" t="n">
-        <v>1.880302071203517</v>
+        <v>1.880763567036991</v>
       </c>
       <c r="L146" t="n">
         <v>22.79439066367491</v>
       </c>
       <c r="M146" t="n">
-        <v>2.446076643315274</v>
-      </c>
-      <c r="N146" t="n">
-        <v>1.289010081981549</v>
-      </c>
-      <c r="O146" t="n">
-        <v>1.867543362648411</v>
-      </c>
+        <v>2.228902580455803</v>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
       <c r="P146" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>-0.6831813820382671</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8956,26 +8704,20 @@
         <v>19</v>
       </c>
       <c r="K147" t="n">
-        <v>1.833191292616835</v>
+        <v>1.833305263923982</v>
       </c>
       <c r="L147" t="n">
         <v>23.08537264490868</v>
       </c>
       <c r="M147" t="n">
-        <v>2.401508938888195</v>
-      </c>
-      <c r="N147" t="n">
-        <v>1.353093274823836</v>
-      </c>
-      <c r="O147" t="n">
-        <v>1.877301106856016</v>
-      </c>
+        <v>2.399449402253348</v>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
       <c r="P147" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>2.349639814203952</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -9015,26 +8757,20 @@
         <v>19</v>
       </c>
       <c r="K148" t="n">
-        <v>1.835108269023008</v>
+        <v>1.835471097545149</v>
       </c>
       <c r="L148" t="n">
         <v>23.28578007667378</v>
       </c>
       <c r="M148" t="n">
-        <v>2.355374210797699</v>
-      </c>
-      <c r="N148" t="n">
-        <v>1.249019127836197</v>
-      </c>
-      <c r="O148" t="n">
-        <v>1.802196669316948</v>
-      </c>
+        <v>2.399449402253348</v>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
       <c r="P148" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>-1.826193570679191</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -9074,26 +8810,20 @@
         <v>19</v>
       </c>
       <c r="K149" t="n">
-        <v>1.837290468265474</v>
+        <v>1.838170620522636</v>
       </c>
       <c r="L149" t="n">
         <v>23.43111776787539</v>
       </c>
       <c r="M149" t="n">
-        <v>2.315226465388985</v>
-      </c>
-      <c r="N149" t="n">
-        <v>1.071318962206051</v>
-      </c>
-      <c r="O149" t="n">
-        <v>1.693272713797518</v>
-      </c>
+        <v>2.53628906525354</v>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
       <c r="P149" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>-8.505289980428831</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -9133,26 +8863,20 @@
         <v>19</v>
       </c>
       <c r="K150" t="n">
-        <v>1.851183425352798</v>
+        <v>1.852734478318536</v>
       </c>
       <c r="L150" t="n">
         <v>23.70802481180992</v>
       </c>
       <c r="M150" t="n">
-        <v>2.457069773380443</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0.9282874515275316</v>
-      </c>
-      <c r="O150" t="n">
-        <v>1.692678612453987</v>
-      </c>
+        <v>2.553200095302242</v>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
       <c r="P150" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>-9.364141056228981</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -9192,26 +8916,20 @@
         <v>19</v>
       </c>
       <c r="K151" t="n">
-        <v>1.851183425352798</v>
+        <v>1.852734478318536</v>
       </c>
       <c r="L151" t="n">
         <v>23.71824889507465</v>
       </c>
       <c r="M151" t="n">
-        <v>2.457069773380443</v>
-      </c>
-      <c r="N151" t="n">
-        <v>0.9282874515275316</v>
-      </c>
-      <c r="O151" t="n">
-        <v>1.692678612453987</v>
-      </c>
+        <v>2.553200095302242</v>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
       <c r="P151" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>-9.364141056228981</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9251,26 +8969,20 @@
         <v>19</v>
       </c>
       <c r="K152" t="n">
-        <v>1.851183425352798</v>
+        <v>1.852734478318536</v>
       </c>
       <c r="L152" t="n">
         <v>23.71833419429876</v>
       </c>
       <c r="M152" t="n">
-        <v>2.457069773380443</v>
-      </c>
-      <c r="N152" t="n">
-        <v>0.9282874515275316</v>
-      </c>
-      <c r="O152" t="n">
-        <v>1.692678612453987</v>
-      </c>
+        <v>2.553200095302242</v>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
       <c r="P152" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>-9.364141056228981</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9310,26 +9022,20 @@
         <v>19</v>
       </c>
       <c r="K153" t="n">
-        <v>1.918307120376766</v>
+        <v>1.914609353839869</v>
       </c>
       <c r="L153" t="n">
         <v>23.88498231768936</v>
       </c>
       <c r="M153" t="n">
-        <v>2.482427983219213</v>
-      </c>
-      <c r="N153" t="n">
-        <v>0.8844761571323866</v>
-      </c>
-      <c r="O153" t="n">
-        <v>1.6834520701758</v>
-      </c>
+        <v>2.525998643457513</v>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
       <c r="P153" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>-13.95080111644884</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9369,26 +9075,20 @@
         <v>19</v>
       </c>
       <c r="K154" t="n">
-        <v>1.985832791947801</v>
+        <v>1.986039459425867</v>
       </c>
       <c r="L154" t="n">
         <v>24.16367053344452</v>
       </c>
       <c r="M154" t="n">
-        <v>2.511628680011507</v>
-      </c>
-      <c r="N154" t="n">
-        <v>0.8922070873695911</v>
-      </c>
-      <c r="O154" t="n">
-        <v>1.701917883690549</v>
-      </c>
+        <v>2.460272776605422</v>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
       <c r="P154" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>-16.6820568123764</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9428,26 +9128,20 @@
         <v>19</v>
       </c>
       <c r="K155" t="n">
-        <v>1.94111181613984</v>
+        <v>1.943612908866282</v>
       </c>
       <c r="L155" t="n">
         <v>24.44971980302625</v>
       </c>
       <c r="M155" t="n">
-        <v>2.552545134477885</v>
-      </c>
-      <c r="N155" t="n">
-        <v>1.210838832206954</v>
-      </c>
-      <c r="O155" t="n">
-        <v>1.881691983342419</v>
-      </c>
+        <v>2.340941256016772</v>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
       <c r="P155" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>-3.157787423416347</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9487,26 +9181,20 @@
         <v>19</v>
       </c>
       <c r="K156" t="n">
-        <v>1.884597235153793</v>
+        <v>1.88775516460374</v>
       </c>
       <c r="L156" t="n">
         <v>24.60424997229683</v>
       </c>
       <c r="M156" t="n">
-        <v>2.549148888523415</v>
-      </c>
-      <c r="N156" t="n">
-        <v>1.265759784093344</v>
-      </c>
-      <c r="O156" t="n">
-        <v>1.907454336308379</v>
-      </c>
+        <v>2.336857632616919</v>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
       <c r="P156" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>1.198303976116311</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9546,26 +9234,20 @@
         <v>19</v>
       </c>
       <c r="K157" t="n">
-        <v>1.884597235153793</v>
+        <v>1.88775516460374</v>
       </c>
       <c r="L157" t="n">
         <v>24.60636313554535</v>
       </c>
       <c r="M157" t="n">
-        <v>2.549148888523415</v>
-      </c>
-      <c r="N157" t="n">
-        <v>1.265759784093344</v>
-      </c>
-      <c r="O157" t="n">
-        <v>1.907454336308379</v>
-      </c>
+        <v>2.336857632616919</v>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
       <c r="P157" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>1.198303976116311</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9605,26 +9287,20 @@
         <v>19</v>
       </c>
       <c r="K158" t="n">
-        <v>1.884597235153793</v>
+        <v>1.809336938530754</v>
       </c>
       <c r="L158" t="n">
         <v>24.65222238718893</v>
       </c>
       <c r="M158" t="n">
-        <v>2.549148888523415</v>
-      </c>
-      <c r="N158" t="n">
-        <v>1.265759784093344</v>
-      </c>
-      <c r="O158" t="n">
-        <v>1.907454336308379</v>
-      </c>
+        <v>2.336857632616919</v>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
       <c r="P158" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>1.198303976116311</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9664,26 +9340,20 @@
         <v>19</v>
       </c>
       <c r="K159" t="n">
-        <v>1.621958698060077</v>
+        <v>1.62660465915978</v>
       </c>
       <c r="L159" t="n">
         <v>24.86089262142548</v>
       </c>
       <c r="M159" t="n">
-        <v>2.515759755719835</v>
-      </c>
-      <c r="N159" t="n">
-        <v>1.296048767498403</v>
-      </c>
-      <c r="O159" t="n">
-        <v>1.905904261609119</v>
-      </c>
+        <v>2.292277987951941</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
       <c r="P159" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>14.89820707517137</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9723,26 +9393,20 @@
         <v>19</v>
       </c>
       <c r="K160" t="n">
-        <v>1.621958698060077</v>
+        <v>1.62660465915978</v>
       </c>
       <c r="L160" t="n">
         <v>24.89659839975873</v>
       </c>
       <c r="M160" t="n">
-        <v>2.515759755719835</v>
-      </c>
-      <c r="N160" t="n">
-        <v>1.296048767498403</v>
-      </c>
-      <c r="O160" t="n">
-        <v>1.905904261609119</v>
-      </c>
+        <v>2.292277987951941</v>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
       <c r="P160" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>14.89820707517137</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9782,26 +9446,20 @@
         <v>19</v>
       </c>
       <c r="K161" t="n">
-        <v>1.379798047976322</v>
+        <v>1.382072456968563</v>
       </c>
       <c r="L161" t="n">
         <v>25.19662060685133</v>
       </c>
       <c r="M161" t="n">
-        <v>2.528679156446047</v>
-      </c>
-      <c r="N161" t="n">
-        <v>1.286869092677173</v>
-      </c>
-      <c r="O161" t="n">
-        <v>1.90777412456161</v>
-      </c>
+        <v>2.256972399806862</v>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
       <c r="P161" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>27.67497838385937</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9841,26 +9499,20 @@
         <v>19</v>
       </c>
       <c r="K162" t="n">
-        <v>1.333362209138855</v>
+        <v>1.33559316674232</v>
       </c>
       <c r="L162" t="n">
         <v>25.288872850738</v>
       </c>
       <c r="M162" t="n">
-        <v>2.533869015876358</v>
-      </c>
-      <c r="N162" t="n">
-        <v>1.233372560532288</v>
-      </c>
-      <c r="O162" t="n">
-        <v>1.883620788204323</v>
-      </c>
+        <v>2.253288682135747</v>
+      </c>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
       <c r="P162" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>29.2128109071272</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9900,26 +9552,20 @@
         <v>19</v>
       </c>
       <c r="K163" t="n">
-        <v>1.333362209138855</v>
+        <v>1.289724165900363</v>
       </c>
       <c r="L163" t="n">
         <v>25.36078544016649</v>
       </c>
       <c r="M163" t="n">
-        <v>2.533869015876358</v>
-      </c>
-      <c r="N163" t="n">
-        <v>1.233372560532288</v>
-      </c>
-      <c r="O163" t="n">
-        <v>1.883620788204323</v>
-      </c>
+        <v>2.253288682135747</v>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
       <c r="P163" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>29.2128109071272</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9959,26 +9605,20 @@
         <v>19</v>
       </c>
       <c r="K164" t="n">
-        <v>1.287433504266253</v>
+        <v>1.289724165900363</v>
       </c>
       <c r="L164" t="n">
         <v>25.41906853424516</v>
       </c>
       <c r="M164" t="n">
-        <v>2.530864023077452</v>
-      </c>
-      <c r="N164" t="n">
-        <v>1.233372560532288</v>
-      </c>
-      <c r="O164" t="n">
-        <v>1.88211829180487</v>
-      </c>
+        <v>2.241708558609957</v>
+      </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
       <c r="P164" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>31.59656808650108</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -10018,26 +9658,20 @@
         <v>19</v>
       </c>
       <c r="K165" t="n">
-        <v>1.211808301441334</v>
+        <v>1.212551325507892</v>
       </c>
       <c r="L165" t="n">
         <v>25.70387559831752</v>
       </c>
       <c r="M165" t="n">
-        <v>2.516545216993899</v>
-      </c>
-      <c r="N165" t="n">
-        <v>0.936908567612344</v>
-      </c>
-      <c r="O165" t="n">
-        <v>1.726726892303122</v>
-      </c>
+        <v>2.274494923648692</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
       <c r="P165" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>29.82049988084596</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -10077,26 +9711,20 @@
         <v>19</v>
       </c>
       <c r="K166" t="n">
-        <v>1.205523507937499</v>
+        <v>1.206739525023695</v>
       </c>
       <c r="L166" t="n">
         <v>25.81182493225029</v>
       </c>
       <c r="M166" t="n">
-        <v>2.516545216993899</v>
-      </c>
-      <c r="N166" t="n">
-        <v>0.936908567612344</v>
-      </c>
-      <c r="O166" t="n">
-        <v>1.726726892303122</v>
-      </c>
+        <v>2.274494923648692</v>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
       <c r="P166" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>30.18447136538411</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -10136,26 +9764,20 @@
         <v>19</v>
       </c>
       <c r="K167" t="n">
-        <v>1.205523507937499</v>
+        <v>1.206739525023695</v>
       </c>
       <c r="L167" t="n">
         <v>25.81325714660946</v>
       </c>
       <c r="M167" t="n">
-        <v>2.516545216993899</v>
-      </c>
-      <c r="N167" t="n">
-        <v>0.936908567612344</v>
-      </c>
-      <c r="O167" t="n">
-        <v>1.726726892303122</v>
-      </c>
+        <v>2.274494923648692</v>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
       <c r="P167" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>30.18447136538411</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -10195,26 +9817,20 @@
         <v>19</v>
       </c>
       <c r="K168" t="n">
-        <v>1.205523507937499</v>
+        <v>1.206739525023695</v>
       </c>
       <c r="L168" t="n">
         <v>25.81381409241026</v>
       </c>
       <c r="M168" t="n">
-        <v>2.516545216993899</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0.936908567612344</v>
-      </c>
-      <c r="O168" t="n">
-        <v>1.726726892303122</v>
-      </c>
+        <v>2.274494923648692</v>
+      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
       <c r="P168" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>30.18447136538411</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10254,26 +9870,20 @@
         <v>19</v>
       </c>
       <c r="K169" t="n">
-        <v>1.1928574441495</v>
+        <v>1.192412560549965</v>
       </c>
       <c r="L169" t="n">
         <v>25.95178898559669</v>
       </c>
       <c r="M169" t="n">
-        <v>2.523017728759505</v>
-      </c>
-      <c r="N169" t="n">
-        <v>0.8539973695115169</v>
-      </c>
-      <c r="O169" t="n">
-        <v>1.688507549135511</v>
-      </c>
+        <v>2.33992287022176</v>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
       <c r="P169" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>29.35433159536516</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10313,26 +9923,20 @@
         <v>19</v>
       </c>
       <c r="K170" t="n">
-        <v>1.16536180842725</v>
+        <v>1.165322041777845</v>
       </c>
       <c r="L170" t="n">
         <v>26.11970280595964</v>
       </c>
       <c r="M170" t="n">
-        <v>2.543958390346354</v>
-      </c>
-      <c r="N170" t="n">
-        <v>0.7864108338360511</v>
-      </c>
-      <c r="O170" t="n">
-        <v>1.665184612091203</v>
-      </c>
+        <v>2.33992287022176</v>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
       <c r="P170" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>30.0160594828135</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10372,26 +9976,20 @@
         <v>19</v>
       </c>
       <c r="K171" t="n">
-        <v>1.16536180842725</v>
+        <v>1.165322041777845</v>
       </c>
       <c r="L171" t="n">
         <v>26.15684461053896</v>
       </c>
       <c r="M171" t="n">
-        <v>2.543958390346354</v>
-      </c>
-      <c r="N171" t="n">
-        <v>0.7864108338360511</v>
-      </c>
-      <c r="O171" t="n">
-        <v>1.665184612091203</v>
-      </c>
+        <v>2.33992287022176</v>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
       <c r="P171" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>30.0160594828135</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10431,26 +10029,20 @@
         <v>19</v>
       </c>
       <c r="K172" t="n">
-        <v>1.236228494084955</v>
+        <v>1.234632837280565</v>
       </c>
       <c r="L172" t="n">
         <v>26.48467882363132</v>
       </c>
       <c r="M172" t="n">
-        <v>2.485677645008055</v>
-      </c>
-      <c r="N172" t="n">
-        <v>0.549182760801554</v>
-      </c>
-      <c r="O172" t="n">
-        <v>1.517430202904805</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
       <c r="P172" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>18.53144271687403</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10490,26 +10082,20 @@
         <v>19</v>
       </c>
       <c r="K173" t="n">
-        <v>1.236228494084955</v>
+        <v>1.234632837280565</v>
       </c>
       <c r="L173" t="n">
         <v>26.55901810614764</v>
       </c>
       <c r="M173" t="n">
-        <v>2.451207524165408</v>
-      </c>
-      <c r="N173" t="n">
-        <v>0.549182760801554</v>
-      </c>
-      <c r="O173" t="n">
-        <v>1.500195142483481</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
       <c r="P173" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>17.5954874751524</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10549,26 +10135,20 @@
         <v>19</v>
       </c>
       <c r="K174" t="n">
-        <v>1.260336599441735</v>
+        <v>1.259479778907701</v>
       </c>
       <c r="L174" t="n">
         <v>26.5770800012127</v>
       </c>
       <c r="M174" t="n">
-        <v>2.451207524165408</v>
-      </c>
-      <c r="N174" t="n">
-        <v>0.549182760801554</v>
-      </c>
-      <c r="O174" t="n">
-        <v>1.500195142483481</v>
-      </c>
+        <v>2.528368514819499</v>
+      </c>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
       <c r="P174" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q174" t="n">
-        <v>15.9884895137492</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10608,26 +10188,20 @@
         <v>19</v>
       </c>
       <c r="K175" t="n">
-        <v>1.297429051340093</v>
+        <v>1.297041515423841</v>
       </c>
       <c r="L175" t="n">
         <v>26.81968738362933</v>
       </c>
       <c r="M175" t="n">
-        <v>2.402168259650153</v>
-      </c>
-      <c r="N175" t="n">
-        <v>0.1500163060053583</v>
-      </c>
-      <c r="O175" t="n">
-        <v>1.276092282827756</v>
-      </c>
+        <v>2.584006862581848</v>
+      </c>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
       <c r="P175" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q175" t="n">
-        <v>-1.672039616528043</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10667,26 +10241,20 @@
         <v>19</v>
       </c>
       <c r="K176" t="n">
-        <v>1.297429051340093</v>
+        <v>1.297041515423841</v>
       </c>
       <c r="L176" t="n">
         <v>26.86547928734959</v>
       </c>
       <c r="M176" t="n">
-        <v>2.402168259650153</v>
-      </c>
-      <c r="N176" t="n">
-        <v>0.1500163060053583</v>
-      </c>
-      <c r="O176" t="n">
-        <v>1.276092282827756</v>
-      </c>
+        <v>2.584006862581848</v>
+      </c>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
       <c r="P176" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>-1.672039616528043</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10726,13 +10294,13 @@
         <v>19</v>
       </c>
       <c r="K177" t="n">
-        <v>1.30326712508255</v>
+        <v>1.30334220224594</v>
       </c>
       <c r="L177" t="n">
         <v>26.9712441052315</v>
       </c>
       <c r="M177" t="n">
-        <v>2.190765346481614</v>
+        <v>2.586709133287388</v>
       </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
@@ -10779,13 +10347,13 @@
         <v>19</v>
       </c>
       <c r="K178" t="n">
-        <v>1.281377167733944</v>
+        <v>1.283448220578055</v>
       </c>
       <c r="L178" t="n">
         <v>27.14455214119267</v>
       </c>
       <c r="M178" t="n">
-        <v>2.123036630767556</v>
+        <v>2.586709133287388</v>
       </c>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
@@ -10832,13 +10400,13 @@
         <v>19</v>
       </c>
       <c r="K179" t="n">
-        <v>1.251783703030703</v>
+        <v>1.254499829613582</v>
       </c>
       <c r="L179" t="n">
         <v>27.20184617145075</v>
       </c>
       <c r="M179" t="n">
-        <v>2.123036630767556</v>
+        <v>2.586709133287388</v>
       </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
@@ -10885,13 +10453,13 @@
         <v>19</v>
       </c>
       <c r="K180" t="n">
-        <v>1.227335525810869</v>
+        <v>1.224959555379384</v>
       </c>
       <c r="L180" t="n">
         <v>27.4540747786318</v>
       </c>
       <c r="M180" t="n">
-        <v>1.992580752593158</v>
+        <v>2.54484718829641</v>
       </c>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
@@ -10938,13 +10506,13 @@
         <v>19</v>
       </c>
       <c r="K181" t="n">
-        <v>1.243950820717568</v>
+        <v>1.241736362431915</v>
       </c>
       <c r="L181" t="n">
         <v>27.61540678756369</v>
       </c>
       <c r="M181" t="n">
-        <v>1.957100819987285</v>
+        <v>2.530712990426041</v>
       </c>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
@@ -10991,13 +10559,13 @@
         <v>19</v>
       </c>
       <c r="K182" t="n">
-        <v>1.243950820717568</v>
+        <v>1.241736362431915</v>
       </c>
       <c r="L182" t="n">
         <v>27.61548192838556</v>
       </c>
       <c r="M182" t="n">
-        <v>1.957100819987285</v>
+        <v>2.530712990426041</v>
       </c>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
@@ -11044,13 +10612,13 @@
         <v>19</v>
       </c>
       <c r="K183" t="n">
-        <v>1.243950820717568</v>
+        <v>1.241736362431915</v>
       </c>
       <c r="L183" t="n">
         <v>27.61548192838556</v>
       </c>
       <c r="M183" t="n">
-        <v>1.957100819987285</v>
+        <v>2.530712990426041</v>
       </c>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
@@ -11097,13 +10665,13 @@
         <v>19</v>
       </c>
       <c r="K184" t="n">
-        <v>1.289010081981549</v>
+        <v>1.289442800577439</v>
       </c>
       <c r="L184" t="n">
         <v>27.78934168734663</v>
       </c>
       <c r="M184" t="n">
-        <v>1.880302071203517</v>
+        <v>2.451535302424364</v>
       </c>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
@@ -11150,13 +10718,13 @@
         <v>19</v>
       </c>
       <c r="K185" t="n">
-        <v>1.289010081981549</v>
+        <v>1.289442800577439</v>
       </c>
       <c r="L185" t="n">
         <v>27.85882769510874</v>
       </c>
       <c r="M185" t="n">
-        <v>1.880302071203517</v>
+        <v>2.451535302424364</v>
       </c>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
@@ -11203,13 +10771,13 @@
         <v>19</v>
       </c>
       <c r="K186" t="n">
-        <v>1.30978613598686</v>
+        <v>1.31326574375713</v>
       </c>
       <c r="L186" t="n">
         <v>27.97316273651501</v>
       </c>
       <c r="M186" t="n">
-        <v>1.833191292616835</v>
+        <v>2.390129634984446</v>
       </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
@@ -11256,13 +10824,13 @@
         <v>19</v>
       </c>
       <c r="K187" t="n">
-        <v>1.30978613598686</v>
+        <v>1.359042505236806</v>
       </c>
       <c r="L187" t="n">
         <v>27.98856193939777</v>
       </c>
       <c r="M187" t="n">
-        <v>1.833191292616835</v>
+        <v>2.390129634984446</v>
       </c>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
@@ -11309,13 +10877,13 @@
         <v>19</v>
       </c>
       <c r="K188" t="n">
-        <v>1.353093274823836</v>
+        <v>1.359042505236806</v>
       </c>
       <c r="L188" t="n">
         <v>28.05964620050748</v>
       </c>
       <c r="M188" t="n">
-        <v>1.833191292616835</v>
+        <v>2.390129634984446</v>
       </c>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
@@ -11362,13 +10930,13 @@
         <v>19</v>
       </c>
       <c r="K189" t="n">
-        <v>1.349097862080286</v>
+        <v>1.351998829157492</v>
       </c>
       <c r="L189" t="n">
         <v>28.11825186873418</v>
       </c>
       <c r="M189" t="n">
-        <v>1.833191292616835</v>
+        <v>2.390129634984446</v>
       </c>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
@@ -11415,13 +10983,13 @@
         <v>19</v>
       </c>
       <c r="K190" t="n">
-        <v>1.349097862080286</v>
+        <v>1.351998829157492</v>
       </c>
       <c r="L190" t="n">
         <v>28.18458074890743</v>
       </c>
       <c r="M190" t="n">
-        <v>1.833191292616835</v>
+        <v>2.339746983234845</v>
       </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
@@ -11468,13 +11036,13 @@
         <v>19</v>
       </c>
       <c r="K191" t="n">
-        <v>1.349097862080286</v>
+        <v>1.351998829157492</v>
       </c>
       <c r="L191" t="n">
         <v>28.18511240330777</v>
       </c>
       <c r="M191" t="n">
-        <v>1.833191292616835</v>
+        <v>2.339746983234845</v>
       </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
@@ -11521,13 +11089,13 @@
         <v>19</v>
       </c>
       <c r="K192" t="n">
-        <v>1.249019127836197</v>
+        <v>1.252221301150578</v>
       </c>
       <c r="L192" t="n">
         <v>28.26821473598177</v>
       </c>
       <c r="M192" t="n">
-        <v>1.835108269023008</v>
+        <v>2.339746983234845</v>
       </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
@@ -11574,13 +11142,13 @@
         <v>19</v>
       </c>
       <c r="K193" t="n">
-        <v>1.146242541840859</v>
+        <v>1.151677425181881</v>
       </c>
       <c r="L193" t="n">
         <v>28.34230266868688</v>
       </c>
       <c r="M193" t="n">
-        <v>1.835108269023008</v>
+        <v>2.311422362296051</v>
       </c>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
@@ -11627,13 +11195,13 @@
         <v>19</v>
       </c>
       <c r="K194" t="n">
-        <v>1.071318962206051</v>
+        <v>1.074753893044807</v>
       </c>
       <c r="L194" t="n">
         <v>28.41870752009863</v>
       </c>
       <c r="M194" t="n">
-        <v>1.837290468265474</v>
+        <v>2.311422362296051</v>
       </c>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
@@ -11680,13 +11248,13 @@
         <v>19</v>
       </c>
       <c r="K195" t="n">
-        <v>0.9282874515275316</v>
+        <v>0.9293217077643242</v>
       </c>
       <c r="L195" t="n">
         <v>28.63423417460503</v>
       </c>
       <c r="M195" t="n">
-        <v>1.851183425352798</v>
+        <v>2.45584612763724</v>
       </c>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
@@ -11733,13 +11301,13 @@
         <v>19</v>
       </c>
       <c r="K196" t="n">
-        <v>0.8844761571323866</v>
+        <v>0.8843090081545558</v>
       </c>
       <c r="L196" t="n">
         <v>28.81488406868647</v>
       </c>
       <c r="M196" t="n">
-        <v>1.918307120376766</v>
+        <v>2.45584612763724</v>
       </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
@@ -11786,13 +11354,13 @@
         <v>19</v>
       </c>
       <c r="K197" t="n">
-        <v>0.8922070873695911</v>
+        <v>0.8918796143983428</v>
       </c>
       <c r="L197" t="n">
         <v>28.98540724636675</v>
       </c>
       <c r="M197" t="n">
-        <v>1.918307120376766</v>
+        <v>2.482296945838069</v>
       </c>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
@@ -11839,13 +11407,13 @@
         <v>19</v>
       </c>
       <c r="K198" t="n">
-        <v>1.145696371936362</v>
+        <v>1.143035239705504</v>
       </c>
       <c r="L198" t="n">
         <v>29.40846794522468</v>
       </c>
       <c r="M198" t="n">
-        <v>1.94111181613984</v>
+        <v>2.552119591261148</v>
       </c>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
@@ -11892,13 +11460,13 @@
         <v>19</v>
       </c>
       <c r="K199" t="n">
-        <v>1.210838832206954</v>
+        <v>1.208876145314666</v>
       </c>
       <c r="L199" t="n">
         <v>29.47347605694008</v>
       </c>
       <c r="M199" t="n">
-        <v>1.94111181613984</v>
+        <v>2.552119591261148</v>
       </c>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
@@ -11945,13 +11513,13 @@
         <v>19</v>
       </c>
       <c r="K200" t="n">
-        <v>1.265759784093344</v>
+        <v>1.265348069603777</v>
       </c>
       <c r="L200" t="n">
         <v>29.68885139127334</v>
       </c>
       <c r="M200" t="n">
-        <v>1.884597235153793</v>
+        <v>2.54962759680487</v>
       </c>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
@@ -11998,13 +11566,13 @@
         <v>19</v>
       </c>
       <c r="K201" t="n">
-        <v>1.265759784093344</v>
+        <v>1.265348069603777</v>
       </c>
       <c r="L201" t="n">
         <v>29.71836867471695</v>
       </c>
       <c r="M201" t="n">
-        <v>1.884597235153793</v>
+        <v>2.54962759680487</v>
       </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
@@ -12051,13 +11619,13 @@
         <v>19</v>
       </c>
       <c r="K202" t="n">
-        <v>1.296048767498403</v>
+        <v>1.298981901047366</v>
       </c>
       <c r="L202" t="n">
         <v>29.92825665953706</v>
       </c>
       <c r="M202" t="n">
-        <v>1.621958698060077</v>
+        <v>2.515616111885459</v>
       </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
@@ -12104,13 +11672,13 @@
         <v>19</v>
       </c>
       <c r="K203" t="n">
-        <v>1.298801741278553</v>
+        <v>1.298981901047366</v>
       </c>
       <c r="L203" t="n">
         <v>29.95990322711403</v>
       </c>
       <c r="M203" t="n">
-        <v>1.621958698060077</v>
+        <v>2.515616111885459</v>
       </c>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
@@ -12157,13 +11725,13 @@
         <v>19</v>
       </c>
       <c r="K204" t="n">
-        <v>1.286869092677173</v>
+        <v>1.287600716901656</v>
       </c>
       <c r="L204" t="n">
         <v>30.06328315923717</v>
       </c>
       <c r="M204" t="n">
-        <v>1.379798047976322</v>
+        <v>2.52834745651818</v>
       </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
@@ -12210,13 +11778,13 @@
         <v>19</v>
       </c>
       <c r="K205" t="n">
-        <v>1.233372560532288</v>
+        <v>1.234526023781353</v>
       </c>
       <c r="L205" t="n">
         <v>30.3825457731479</v>
       </c>
       <c r="M205" t="n">
-        <v>1.333362209138855</v>
+        <v>2.533854113018922</v>
       </c>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
@@ -12263,13 +11831,13 @@
         <v>19</v>
       </c>
       <c r="K206" t="n">
-        <v>1.233372560532288</v>
+        <v>1.234526023781353</v>
       </c>
       <c r="L206" t="n">
         <v>30.39023084222564</v>
       </c>
       <c r="M206" t="n">
-        <v>1.287433504266253</v>
+        <v>2.533854113018922</v>
       </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
@@ -12316,13 +11884,13 @@
         <v>19</v>
       </c>
       <c r="K207" t="n">
-        <v>1.13176711732786</v>
+        <v>1.135750742934406</v>
       </c>
       <c r="L207" t="n">
         <v>30.54762528394958</v>
       </c>
       <c r="M207" t="n">
-        <v>1.287433504266253</v>
+        <v>2.531204737504585</v>
       </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
@@ -12369,13 +11937,13 @@
         <v>19</v>
       </c>
       <c r="K208" t="n">
-        <v>0.936908567612344</v>
+        <v>0.9438187947621866</v>
       </c>
       <c r="L208" t="n">
         <v>30.79318609575494</v>
       </c>
       <c r="M208" t="n">
-        <v>1.205523507937499</v>
+        <v>2.52260041570954</v>
       </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
@@ -12422,13 +11990,13 @@
         <v>19</v>
       </c>
       <c r="K209" t="n">
-        <v>0.8539973695115169</v>
+        <v>0.8586149336110689</v>
       </c>
       <c r="L209" t="n">
         <v>30.93382442441887</v>
       </c>
       <c r="M209" t="n">
-        <v>1.1928574441495</v>
+        <v>2.52260041570954</v>
       </c>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
@@ -12475,13 +12043,13 @@
         <v>19</v>
       </c>
       <c r="K210" t="n">
-        <v>0.822075033593868</v>
+        <v>0.82347174497717</v>
       </c>
       <c r="L210" t="n">
         <v>30.98380716405565</v>
       </c>
       <c r="M210" t="n">
-        <v>1.1928574441495</v>
+        <v>2.52260041570954</v>
       </c>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
@@ -12528,13 +12096,13 @@
         <v>19</v>
       </c>
       <c r="K211" t="n">
-        <v>0.822075033593868</v>
+        <v>0.82347174497717</v>
       </c>
       <c r="L211" t="n">
         <v>30.9842111619284</v>
       </c>
       <c r="M211" t="n">
-        <v>1.1928574441495</v>
+        <v>2.52260041570954</v>
       </c>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
@@ -12581,13 +12149,13 @@
         <v>19</v>
       </c>
       <c r="K212" t="n">
-        <v>0.7864108338360511</v>
+        <v>0.7391853344810749</v>
       </c>
       <c r="L212" t="n">
         <v>31.1487463046173</v>
       </c>
       <c r="M212" t="n">
-        <v>1.16536180842725</v>
+        <v>2.543868584742552</v>
       </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
@@ -12634,13 +12202,13 @@
         <v>19</v>
       </c>
       <c r="K213" t="n">
-        <v>0.7371944434193791</v>
+        <v>0.7391853344810749</v>
       </c>
       <c r="L213" t="n">
         <v>31.19902718432386</v>
       </c>
       <c r="M213" t="n">
-        <v>1.16536180842725</v>
+        <v>2.543868584742552</v>
       </c>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
@@ -12687,13 +12255,13 @@
         <v>19</v>
       </c>
       <c r="K214" t="n">
-        <v>0.6750310988820618</v>
+        <v>0.678101286899057</v>
       </c>
       <c r="L214" t="n">
         <v>31.27042506594725</v>
       </c>
       <c r="M214" t="n">
-        <v>1.16536180842725</v>
+        <v>2.543868584742552</v>
       </c>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
@@ -12740,13 +12308,13 @@
         <v>19</v>
       </c>
       <c r="K215" t="n">
-        <v>0.6750310988820618</v>
+        <v>0.678101286899057</v>
       </c>
       <c r="L215" t="n">
         <v>31.31077903096681</v>
       </c>
       <c r="M215" t="n">
-        <v>1.16536180842725</v>
+        <v>2.543868584742552</v>
       </c>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
@@ -12793,13 +12361,13 @@
         <v>19</v>
       </c>
       <c r="K216" t="n">
-        <v>0.549182760801554</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="L216" t="n">
         <v>31.51725877529833</v>
       </c>
       <c r="M216" t="n">
-        <v>1.236228494084955</v>
+        <v>2.453235713426281</v>
       </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
@@ -12846,13 +12414,13 @@
         <v>19</v>
       </c>
       <c r="K217" t="n">
-        <v>0.549182760801554</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="L217" t="n">
         <v>31.51976949532537</v>
       </c>
       <c r="M217" t="n">
-        <v>1.236228494084955</v>
+        <v>2.453235713426281</v>
       </c>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
@@ -12899,13 +12467,13 @@
         <v>19</v>
       </c>
       <c r="K218" t="n">
-        <v>0.549182760801554</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="L218" t="n">
         <v>31.54090212492537</v>
       </c>
       <c r="M218" t="n">
-        <v>1.236228494084955</v>
+        <v>2.453235713426281</v>
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
@@ -12952,13 +12520,13 @@
         <v>19</v>
       </c>
       <c r="K219" t="n">
-        <v>0.549182760801554</v>
+        <v>0.5523719819007573</v>
       </c>
       <c r="L219" t="n">
         <v>31.54099271896593</v>
       </c>
       <c r="M219" t="n">
-        <v>1.236228494084955</v>
+        <v>2.453235713426281</v>
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
@@ -13005,13 +12573,13 @@
         <v>19</v>
       </c>
       <c r="K220" t="n">
-        <v>0.1500163060053583</v>
+        <v>0.155202974904865</v>
       </c>
       <c r="L220" t="n">
         <v>31.92043866751308</v>
       </c>
       <c r="M220" t="n">
-        <v>1.30326712508255</v>
+        <v>2.194344862432881</v>
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
